--- a/data/Movie_vocab.xlsx
+++ b/data/Movie_vocab.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="882">
   <si>
     <t>german_word</t>
   </si>
@@ -51,6 +51,2616 @@
   </si>
   <si>
     <t>note</t>
+  </si>
+  <si>
+    <t>bleib</t>
+  </si>
+  <si>
+    <t>blaib</t>
+  </si>
+  <si>
+    <t>stay</t>
+  </si>
+  <si>
+    <t>Bitte bleib hier.</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>sleep</t>
+  </si>
+  <si>
+    <t>verb</t>
+  </si>
+  <si>
+    <t>🧍</t>
+  </si>
+  <si>
+    <t>person waiting standing still staying place</t>
+  </si>
+  <si>
+    <t>Verb</t>
+  </si>
+  <si>
+    <t>stehen</t>
+  </si>
+  <si>
+    <t>shtay-en</t>
+  </si>
+  <si>
+    <t>to stand</t>
+  </si>
+  <si>
+    <t>Ich stehe hier.</t>
+  </si>
+  <si>
+    <t>sit</t>
+  </si>
+  <si>
+    <t>stand</t>
+  </si>
+  <si>
+    <t>🧍‍♂️</t>
+  </si>
+  <si>
+    <t>person standing upright human posture</t>
+  </si>
+  <si>
+    <t>denken</t>
+  </si>
+  <si>
+    <t>denk-en</t>
+  </si>
+  <si>
+    <t>to think</t>
+  </si>
+  <si>
+    <t>Ich denke viel.</t>
+  </si>
+  <si>
+    <t>think</t>
+  </si>
+  <si>
+    <t>eat</t>
+  </si>
+  <si>
+    <t>drive</t>
+  </si>
+  <si>
+    <t>🤔</t>
+  </si>
+  <si>
+    <t>person thinking brain thought idea</t>
+  </si>
+  <si>
+    <t>vor</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>before / in front of</t>
+  </si>
+  <si>
+    <t>Er steht vor dem Haus.</t>
+  </si>
+  <si>
+    <t>behind</t>
+  </si>
+  <si>
+    <t>before</t>
+  </si>
+  <si>
+    <t>under</t>
+  </si>
+  <si>
+    <t>over</t>
+  </si>
+  <si>
+    <t>preposition</t>
+  </si>
+  <si>
+    <t>➡️</t>
+  </si>
+  <si>
+    <t>person standing in front house entrance</t>
+  </si>
+  <si>
+    <t>Preposition</t>
+  </si>
+  <si>
+    <t>hübsch</t>
+  </si>
+  <si>
+    <t>hoobsh</t>
+  </si>
+  <si>
+    <t>pretty</t>
+  </si>
+  <si>
+    <t>Das Mädchen ist hübsch.</t>
+  </si>
+  <si>
+    <t>ugly</t>
+  </si>
+  <si>
+    <t>tall</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>adjective</t>
+  </si>
+  <si>
+    <t>😊</t>
+  </si>
+  <si>
+    <t>beautiful woman pretty girl smiling portrait</t>
+  </si>
+  <si>
+    <t>Adjective</t>
+  </si>
+  <si>
+    <t>besten</t>
+  </si>
+  <si>
+    <t>bes-ten</t>
+  </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>Das ist am besten.</t>
+  </si>
+  <si>
+    <t>worst</t>
+  </si>
+  <si>
+    <t>better</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>🏆</t>
+  </si>
+  <si>
+    <t>gold trophy first place winner champion</t>
+  </si>
+  <si>
+    <t>aussieht</t>
+  </si>
+  <si>
+    <t>ows-zeet</t>
+  </si>
+  <si>
+    <t>looks / appears</t>
+  </si>
+  <si>
+    <t>Er sieht gut aus.</t>
+  </si>
+  <si>
+    <t>looks</t>
+  </si>
+  <si>
+    <t>runs</t>
+  </si>
+  <si>
+    <t>eats</t>
+  </si>
+  <si>
+    <t>writes</t>
+  </si>
+  <si>
+    <t>👀</t>
+  </si>
+  <si>
+    <t>person face appearance looking mirror portrait</t>
+  </si>
+  <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>Der Mann ist arm.</t>
+  </si>
+  <si>
+    <t>rich</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>💸</t>
+  </si>
+  <si>
+    <t>poor homeless person empty wallet poverty</t>
+  </si>
+  <si>
+    <t>echt</t>
+  </si>
+  <si>
+    <t>ekht</t>
+  </si>
+  <si>
+    <t>real / really</t>
+  </si>
+  <si>
+    <t>Das ist echt gut.</t>
+  </si>
+  <si>
+    <t>fake</t>
+  </si>
+  <si>
+    <t>real</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>real object authentic genuine original item</t>
+  </si>
+  <si>
+    <t>süß</t>
+  </si>
+  <si>
+    <t>zues</t>
+  </si>
+  <si>
+    <t>sweet / cute</t>
+  </si>
+  <si>
+    <t>Der Hund ist süß.</t>
+  </si>
+  <si>
+    <t>sour</t>
+  </si>
+  <si>
+    <t>bitter</t>
+  </si>
+  <si>
+    <t>sweet</t>
+  </si>
+  <si>
+    <t>salty</t>
+  </si>
+  <si>
+    <t>🍭</t>
+  </si>
+  <si>
+    <t>cute puppy kitten baby teddy bear</t>
+  </si>
+  <si>
+    <t>schon</t>
+  </si>
+  <si>
+    <t>shohn</t>
+  </si>
+  <si>
+    <t>already</t>
+  </si>
+  <si>
+    <t>Ich habe schon gegessen.</t>
+  </si>
+  <si>
+    <t>never</t>
+  </si>
+  <si>
+    <t>later</t>
+  </si>
+  <si>
+    <t>tomorrow</t>
+  </si>
+  <si>
+    <t>adverb</t>
+  </si>
+  <si>
+    <t>⏰</t>
+  </si>
+  <si>
+    <t>person finished meal empty plate satisfied</t>
+  </si>
+  <si>
+    <t>Adverb</t>
+  </si>
+  <si>
+    <t>hör</t>
+  </si>
+  <si>
+    <t>hoer</t>
+  </si>
+  <si>
+    <t>listen</t>
+  </si>
+  <si>
+    <t>Bitte hör zu.</t>
+  </si>
+  <si>
+    <t>jump</t>
+  </si>
+  <si>
+    <t>👂</t>
+  </si>
+  <si>
+    <t>person listening ear headphones conversation</t>
+  </si>
+  <si>
+    <t>derzeit</t>
+  </si>
+  <si>
+    <t>dayr-tsite</t>
+  </si>
+  <si>
+    <t>currently</t>
+  </si>
+  <si>
+    <t>Ich arbeite derzeit hier.</t>
+  </si>
+  <si>
+    <t>now</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>soon</t>
+  </si>
+  <si>
+    <t>📅</t>
+  </si>
+  <si>
+    <t>calendar current date today present time</t>
+  </si>
+  <si>
+    <t>verlagern</t>
+  </si>
+  <si>
+    <t>fer-lah-gern</t>
+  </si>
+  <si>
+    <t>to shift / move</t>
+  </si>
+  <si>
+    <t>Wir verlagern das Projekt.</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>shift</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>🔄</t>
+  </si>
+  <si>
+    <t>moving boxes relocation transfer workplace</t>
+  </si>
+  <si>
+    <t>auf</t>
+  </si>
+  <si>
+    <t>owf</t>
+  </si>
+  <si>
+    <t>on / onto</t>
+  </si>
+  <si>
+    <t>Das Buch liegt auf dem Tisch.</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>between</t>
+  </si>
+  <si>
+    <t>⬆️</t>
+  </si>
+  <si>
+    <t>book on table object surface placement</t>
+  </si>
+  <si>
+    <t>solltest</t>
+  </si>
+  <si>
+    <t>zol-test</t>
+  </si>
+  <si>
+    <t>should</t>
+  </si>
+  <si>
+    <t>Du solltest lernen.</t>
+  </si>
+  <si>
+    <t>must</t>
+  </si>
+  <si>
+    <t>can</t>
+  </si>
+  <si>
+    <t>will</t>
+  </si>
+  <si>
+    <t>📚</t>
+  </si>
+  <si>
+    <t>student studying advice teacher homework</t>
+  </si>
+  <si>
+    <t>Modal Verb</t>
+  </si>
+  <si>
+    <t>Idioten</t>
+  </si>
+  <si>
+    <t>idi-oh-ten</t>
+  </si>
+  <si>
+    <t>idiots</t>
+  </si>
+  <si>
+    <t>Die Idioten lachen laut.</t>
+  </si>
+  <si>
+    <t>teachers</t>
+  </si>
+  <si>
+    <t>friends</t>
+  </si>
+  <si>
+    <t>doctors</t>
+  </si>
+  <si>
+    <t>noun</t>
+  </si>
+  <si>
+    <t>🤦</t>
+  </si>
+  <si>
+    <t>foolish people making mistakes silly group laughing</t>
+  </si>
+  <si>
+    <t>Noun (Plural)</t>
+  </si>
+  <si>
+    <t>nur</t>
+  </si>
+  <si>
+    <t>noor</t>
+  </si>
+  <si>
+    <t>only</t>
+  </si>
+  <si>
+    <t>Ich habe nur einen Euro.</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>many</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>1️⃣</t>
+  </si>
+  <si>
+    <t>single coin one item only quantity limited</t>
+  </si>
+  <si>
+    <t>einlassen</t>
+  </si>
+  <si>
+    <t>ine-lass-en</t>
+  </si>
+  <si>
+    <t>to get involved</t>
+  </si>
+  <si>
+    <t>Er will sich nicht einlassen.</t>
+  </si>
+  <si>
+    <t>enter</t>
+  </si>
+  <si>
+    <t>leave</t>
+  </si>
+  <si>
+    <t>get involved</t>
+  </si>
+  <si>
+    <t>🚪</t>
+  </si>
+  <si>
+    <t>two people discussion relationship interaction involvement</t>
+  </si>
+  <si>
+    <t>einfach</t>
+  </si>
+  <si>
+    <t>ine-fakh</t>
+  </si>
+  <si>
+    <t>simple / easy</t>
+  </si>
+  <si>
+    <t>Deutsch ist einfach.</t>
+  </si>
+  <si>
+    <t>difficult</t>
+  </si>
+  <si>
+    <t>simple</t>
+  </si>
+  <si>
+    <t>expensive</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>👌</t>
+  </si>
+  <si>
+    <t>easy task simple design beginner learning</t>
+  </si>
+  <si>
+    <t>jetzt</t>
+  </si>
+  <si>
+    <t>yetst</t>
+  </si>
+  <si>
+    <t>Ich gehe jetzt nach Hause.</t>
+  </si>
+  <si>
+    <t>person checking clock current time now</t>
+  </si>
+  <si>
+    <t>diese</t>
+  </si>
+  <si>
+    <t>dee-zeh</t>
+  </si>
+  <si>
+    <t>this/these</t>
+  </si>
+  <si>
+    <t>Diese Frau ist nett.</t>
+  </si>
+  <si>
+    <t>that</t>
+  </si>
+  <si>
+    <t>determiner</t>
+  </si>
+  <si>
+    <t>👉</t>
+  </si>
+  <si>
+    <t>woman pointing object nearby person item</t>
+  </si>
+  <si>
+    <t>Demonstrative Word</t>
+  </si>
+  <si>
+    <t>super</t>
+  </si>
+  <si>
+    <t>zoo-per</t>
+  </si>
+  <si>
+    <t>great/awesome</t>
+  </si>
+  <si>
+    <t>Das ist super!</t>
+  </si>
+  <si>
+    <t>terrible</t>
+  </si>
+  <si>
+    <t>slow</t>
+  </si>
+  <si>
+    <t>🌟</t>
+  </si>
+  <si>
+    <t>happy person thumbs up success celebration</t>
+  </si>
+  <si>
+    <t>gekrobt</t>
+  </si>
+  <si>
+    <t>geh-krobt</t>
+  </si>
+  <si>
+    <t>crawled (likely misspelling/slang)</t>
+  </si>
+  <si>
+    <t>Das Tier ist gekrobt.</t>
+  </si>
+  <si>
+    <t>flew</t>
+  </si>
+  <si>
+    <t>swam</t>
+  </si>
+  <si>
+    <t>crawled</t>
+  </si>
+  <si>
+    <t>jumped</t>
+  </si>
+  <si>
+    <t>🐛</t>
+  </si>
+  <si>
+    <t>crawling insect bug ground movement</t>
+  </si>
+  <si>
+    <t>tut</t>
+  </si>
+  <si>
+    <t>tuot</t>
+  </si>
+  <si>
+    <t>does (from tun)</t>
+  </si>
+  <si>
+    <t>Das tut weh.</t>
+  </si>
+  <si>
+    <t>does</t>
+  </si>
+  <si>
+    <t>sleeps</t>
+  </si>
+  <si>
+    <t>⚙️</t>
+  </si>
+  <si>
+    <t>person performing action working task</t>
+  </si>
+  <si>
+    <t>leid</t>
+  </si>
+  <si>
+    <t>laidt</t>
+  </si>
+  <si>
+    <t>sorry/pain</t>
+  </si>
+  <si>
+    <t>Es tut mir leid.</t>
+  </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t>sorry</t>
+  </si>
+  <si>
+    <t>fast</t>
+  </si>
+  <si>
+    <t>late</t>
+  </si>
+  <si>
+    <t>😔</t>
+  </si>
+  <si>
+    <t>sad person apologizing regret emotion</t>
+  </si>
+  <si>
+    <t>Expression Component</t>
+  </si>
+  <si>
+    <t>Bemerkung</t>
+  </si>
+  <si>
+    <t>beh-mer-koong</t>
+  </si>
+  <si>
+    <t>comment/remark</t>
+  </si>
+  <si>
+    <t>Das ist eine Bemerkung.</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>answer</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>📝</t>
+  </si>
+  <si>
+    <t>person speaking note comment discussion</t>
+  </si>
+  <si>
+    <t>Die</t>
+  </si>
+  <si>
+    <t>gar</t>
+  </si>
+  <si>
+    <t>at all</t>
+  </si>
+  <si>
+    <t>Das ist gar nicht schwer.</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <t>sometimes</t>
+  </si>
+  <si>
+    <t>often</t>
+  </si>
+  <si>
+    <t>❌</t>
+  </si>
+  <si>
+    <t>person shaking head negative response</t>
+  </si>
+  <si>
+    <t>weil</t>
+  </si>
+  <si>
+    <t>vile</t>
+  </si>
+  <si>
+    <t>because</t>
+  </si>
+  <si>
+    <t>Ich lerne, weil ich Deutsch mag.</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>but</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>conjunction</t>
+  </si>
+  <si>
+    <t>🔗</t>
+  </si>
+  <si>
+    <t>person explaining reason cause effect</t>
+  </si>
+  <si>
+    <t>Conjunction</t>
+  </si>
+  <si>
+    <t>Zwerg</t>
+  </si>
+  <si>
+    <t>tsverg</t>
+  </si>
+  <si>
+    <t>dwarf</t>
+  </si>
+  <si>
+    <t>Der Zwerg ist klein.</t>
+  </si>
+  <si>
+    <t>giant</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>teacher</t>
+  </si>
+  <si>
+    <t>🧙</t>
+  </si>
+  <si>
+    <t>fantasy dwarf small person beard</t>
+  </si>
+  <si>
+    <t>Der</t>
+  </si>
+  <si>
+    <t>soll</t>
+  </si>
+  <si>
+    <t>zoll</t>
+  </si>
+  <si>
+    <t>Er soll kommen.</t>
+  </si>
+  <si>
+    <t>wants</t>
+  </si>
+  <si>
+    <t>📋</t>
+  </si>
+  <si>
+    <t>person receiving instruction advice recommendation</t>
+  </si>
+  <si>
+    <t>sich</t>
+  </si>
+  <si>
+    <t>zikh</t>
+  </si>
+  <si>
+    <t>oneself</t>
+  </si>
+  <si>
+    <t>Er freut sich.</t>
+  </si>
+  <si>
+    <t>myself</t>
+  </si>
+  <si>
+    <t>yourself</t>
+  </si>
+  <si>
+    <t>themself</t>
+  </si>
+  <si>
+    <t>pronoun</t>
+  </si>
+  <si>
+    <t>🪞</t>
+  </si>
+  <si>
+    <t>person looking in mirror reflection</t>
+  </si>
+  <si>
+    <t>Reflexive Pronoun</t>
+  </si>
+  <si>
+    <t>mal</t>
+  </si>
+  <si>
+    <t>mahl</t>
+  </si>
+  <si>
+    <t>once/just</t>
+  </si>
+  <si>
+    <t>Komm mal her!</t>
+  </si>
+  <si>
+    <t>👋</t>
+  </si>
+  <si>
+    <t>person calling someone nearby gesture</t>
+  </si>
+  <si>
+    <t>Particle/Adverb</t>
+  </si>
+  <si>
+    <t>schiebe</t>
+  </si>
+  <si>
+    <t>shee-beh</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>Ich schiebe den Wagen.</t>
+  </si>
+  <si>
+    <t>pull</t>
+  </si>
+  <si>
+    <t>throw</t>
+  </si>
+  <si>
+    <t>catch</t>
+  </si>
+  <si>
+    <t>🛒</t>
+  </si>
+  <si>
+    <t>person pushing shopping cart trolley</t>
+  </si>
+  <si>
+    <t>abschneiden</t>
+  </si>
+  <si>
+    <t>ab-shny-den</t>
+  </si>
+  <si>
+    <t>to cut off</t>
+  </si>
+  <si>
+    <t>Er schneidet das Papier ab.</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>cut off</t>
+  </si>
+  <si>
+    <t>paint</t>
+  </si>
+  <si>
+    <t>write</t>
+  </si>
+  <si>
+    <t>✂️</t>
+  </si>
+  <si>
+    <t>scissors cutting paper craft activity</t>
+  </si>
+  <si>
+    <t>Größentechnisch</t>
+  </si>
+  <si>
+    <t>groe-sen-tekh-nish</t>
+  </si>
+  <si>
+    <t>size-wise</t>
+  </si>
+  <si>
+    <t>Größentechnisch passt es.</t>
+  </si>
+  <si>
+    <t>color-wise</t>
+  </si>
+  <si>
+    <t>price-wise</t>
+  </si>
+  <si>
+    <t>time-wise</t>
+  </si>
+  <si>
+    <t>📏</t>
+  </si>
+  <si>
+    <t>measuring tape size comparison dimensions</t>
+  </si>
+  <si>
+    <t>war</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>was</t>
+  </si>
+  <si>
+    <t>Er war gestern hier.</t>
+  </si>
+  <si>
+    <t>is</t>
+  </si>
+  <si>
+    <t>be</t>
+  </si>
+  <si>
+    <t>person standing in past memory scene</t>
+  </si>
+  <si>
+    <t>Verb (sein - past)</t>
+  </si>
+  <si>
+    <t>unhöflich</t>
+  </si>
+  <si>
+    <t>oon-hoef-likh</t>
+  </si>
+  <si>
+    <t>rude</t>
+  </si>
+  <si>
+    <t>Das war unhöflich.</t>
+  </si>
+  <si>
+    <t>polite</t>
+  </si>
+  <si>
+    <t>friendly</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>😒</t>
+  </si>
+  <si>
+    <t>person being rude bad manners argument</t>
+  </si>
+  <si>
+    <t>aber</t>
+  </si>
+  <si>
+    <t>ah-ber</t>
+  </si>
+  <si>
+    <t>Ich komme, aber später.</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>two choices contrast decision discussion</t>
+  </si>
+  <si>
+    <t>kannst</t>
+  </si>
+  <si>
+    <t>kanst</t>
+  </si>
+  <si>
+    <t>Kannst du helfen?</t>
+  </si>
+  <si>
+    <t>want</t>
+  </si>
+  <si>
+    <t>💪</t>
+  </si>
+  <si>
+    <t>person helping ability skill action</t>
+  </si>
+  <si>
+    <t>Verb (können)</t>
+  </si>
+  <si>
+    <t>laut</t>
+  </si>
+  <si>
+    <t>lowt</t>
+  </si>
+  <si>
+    <t>loud</t>
+  </si>
+  <si>
+    <t>Die Musik ist laut.</t>
+  </si>
+  <si>
+    <t>quiet</t>
+  </si>
+  <si>
+    <t>🔊</t>
+  </si>
+  <si>
+    <t>loud speaker music noise volume</t>
+  </si>
+  <si>
+    <t>sagen</t>
+  </si>
+  <si>
+    <t>zah-gen</t>
+  </si>
+  <si>
+    <t>to say</t>
+  </si>
+  <si>
+    <t>Bitte sag die Wahrheit.</t>
+  </si>
+  <si>
+    <t>say</t>
+  </si>
+  <si>
+    <t>💬</t>
+  </si>
+  <si>
+    <t>person talking speech conversation dialogue</t>
+  </si>
+  <si>
+    <t>Frechdachs</t>
+  </si>
+  <si>
+    <t>frekh-daks</t>
+  </si>
+  <si>
+    <t>cheeky person</t>
+  </si>
+  <si>
+    <t>Du kleiner Frechdachs!</t>
+  </si>
+  <si>
+    <t>genius</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>😏</t>
+  </si>
+  <si>
+    <t>mischievous child playful smile prank</t>
+  </si>
+  <si>
+    <t>warte</t>
+  </si>
+  <si>
+    <t>var-te</t>
+  </si>
+  <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>Bitte warte hier.</t>
+  </si>
+  <si>
+    <t>⏳</t>
+  </si>
+  <si>
+    <t>person waiting bus stop patience</t>
+  </si>
+  <si>
+    <t>Scherz</t>
+  </si>
+  <si>
+    <t>sherts</t>
+  </si>
+  <si>
+    <t>joke</t>
+  </si>
+  <si>
+    <t>Das war nur ein Scherz.</t>
+  </si>
+  <si>
+    <t>truth</t>
+  </si>
+  <si>
+    <t>car</t>
+  </si>
+  <si>
+    <t>😂</t>
+  </si>
+  <si>
+    <t>people laughing funny joke comedy</t>
+  </si>
+  <si>
+    <t>über</t>
+  </si>
+  <si>
+    <t>ue-ber</t>
+  </si>
+  <si>
+    <t>about/over</t>
+  </si>
+  <si>
+    <t>Wir sprechen über Deutsch.</t>
+  </si>
+  <si>
+    <t>over/about</t>
+  </si>
+  <si>
+    <t>🌉</t>
+  </si>
+  <si>
+    <t>bridge over river discussion topic</t>
+  </si>
+  <si>
+    <t>machten</t>
+  </si>
+  <si>
+    <t>makh-ten</t>
+  </si>
+  <si>
+    <t>did/made</t>
+  </si>
+  <si>
+    <t>Was machten sie gestern?</t>
+  </si>
+  <si>
+    <t>will do</t>
+  </si>
+  <si>
+    <t>sleeped</t>
+  </si>
+  <si>
+    <t>ran</t>
+  </si>
+  <si>
+    <t>🛠️</t>
+  </si>
+  <si>
+    <t>people working creating project teamwork</t>
+  </si>
+  <si>
+    <t>Verb (machen - past)</t>
+  </si>
+  <si>
+    <t>alle</t>
+  </si>
+  <si>
+    <t>al-le</t>
+  </si>
+  <si>
+    <t>everyone/all</t>
+  </si>
+  <si>
+    <t>Alle sind hier.</t>
+  </si>
+  <si>
+    <t>nobody</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>everyone</t>
+  </si>
+  <si>
+    <t>👥</t>
+  </si>
+  <si>
+    <t>group of people crowd gathering together</t>
+  </si>
+  <si>
+    <t>Pronoun</t>
+  </si>
+  <si>
+    <t>immer</t>
+  </si>
+  <si>
+    <t>im-mer</t>
+  </si>
+  <si>
+    <t>Er kommt immer pünktlich.</t>
+  </si>
+  <si>
+    <t>rarely</t>
+  </si>
+  <si>
+    <t>♾️</t>
+  </si>
+  <si>
+    <t>repeating calendar daily routine habit</t>
+  </si>
+  <si>
+    <t>Witze</t>
+  </si>
+  <si>
+    <t>vit-se</t>
+  </si>
+  <si>
+    <t>jokes</t>
+  </si>
+  <si>
+    <t>Die Witze sind lustig.</t>
+  </si>
+  <si>
+    <t>books</t>
+  </si>
+  <si>
+    <t>cars</t>
+  </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>🤣</t>
+  </si>
+  <si>
+    <t>group laughing funny jokes comedy show</t>
+  </si>
+  <si>
+    <t>Die (Plural)</t>
+  </si>
+  <si>
+    <t>glaube</t>
+  </si>
+  <si>
+    <t>glow-be</t>
+  </si>
+  <si>
+    <t>believe/think</t>
+  </si>
+  <si>
+    <t>Ich glaube dir.</t>
+  </si>
+  <si>
+    <t>believe</t>
+  </si>
+  <si>
+    <t>forget</t>
+  </si>
+  <si>
+    <t>hate</t>
+  </si>
+  <si>
+    <t>break</t>
+  </si>
+  <si>
+    <t>person trusting thinking opinion belief</t>
+  </si>
+  <si>
+    <t>definitiv</t>
+  </si>
+  <si>
+    <t>de-fi-ni-teev</t>
+  </si>
+  <si>
+    <t>definitely</t>
+  </si>
+  <si>
+    <t>Das ist definitiv richtig.</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>checkmark certainty confidence confirmation success</t>
+  </si>
+  <si>
+    <t>verliebt</t>
+  </si>
+  <si>
+    <t>fer-leept</t>
+  </si>
+  <si>
+    <t>in love</t>
+  </si>
+  <si>
+    <t>Er ist verliebt.</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>bored</t>
+  </si>
+  <si>
+    <t>❤️</t>
+  </si>
+  <si>
+    <t>couple romantic love hearts relationship</t>
+  </si>
+  <si>
+    <t>Gefühl</t>
+  </si>
+  <si>
+    <t>geh-fuel</t>
+  </si>
+  <si>
+    <t>feeling/emotion</t>
+  </si>
+  <si>
+    <t>Ich habe ein gutes Gefühl.</t>
+  </si>
+  <si>
+    <t>feeling</t>
+  </si>
+  <si>
+    <t>das</t>
+  </si>
+  <si>
+    <t>💭</t>
+  </si>
+  <si>
+    <t>person showing emotion feelings mood expression</t>
+  </si>
+  <si>
+    <t>Noun</t>
+  </si>
+  <si>
+    <t>auch</t>
+  </si>
+  <si>
+    <t>owkh</t>
+  </si>
+  <si>
+    <t>also/too</t>
+  </si>
+  <si>
+    <t>Ich komme auch mit.</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
+    <t>➕</t>
+  </si>
+  <si>
+    <t>group of friends together inclusion participation</t>
+  </si>
+  <si>
+    <t>mag</t>
+  </si>
+  <si>
+    <t>mahk</t>
+  </si>
+  <si>
+    <t>like</t>
+  </si>
+  <si>
+    <t>Ich mag Pizza.</t>
+  </si>
+  <si>
+    <t>person enjoying food hobby preference</t>
+  </si>
+  <si>
+    <t>Verb (mögen)</t>
+  </si>
+  <si>
+    <t>wie beneidenswert</t>
+  </si>
+  <si>
+    <t>vee be-nide-ens-vert</t>
+  </si>
+  <si>
+    <t>how enviable</t>
+  </si>
+  <si>
+    <t>Das ist wie beneidenswert.</t>
+  </si>
+  <si>
+    <t>how sad</t>
+  </si>
+  <si>
+    <t>how strange</t>
+  </si>
+  <si>
+    <t>how boring</t>
+  </si>
+  <si>
+    <t>phrase</t>
+  </si>
+  <si>
+    <t>😮</t>
+  </si>
+  <si>
+    <t>person admiring someone success achievement lifestyle</t>
+  </si>
+  <si>
+    <t>Phrase</t>
+  </si>
+  <si>
+    <t>wieso</t>
+  </si>
+  <si>
+    <t>vee-zoh</t>
+  </si>
+  <si>
+    <t>why</t>
+  </si>
+  <si>
+    <t>Wieso lachst du?</t>
+  </si>
+  <si>
+    <t>when</t>
+  </si>
+  <si>
+    <t>where</t>
+  </si>
+  <si>
+    <t>who</t>
+  </si>
+  <si>
+    <t>❓</t>
+  </si>
+  <si>
+    <t>person asking question curiosity confusion</t>
+  </si>
+  <si>
+    <t>Question Word</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>mahn</t>
+  </si>
+  <si>
+    <t>one/people</t>
+  </si>
+  <si>
+    <t>Man lernt jeden Tag.</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>she</t>
+  </si>
+  <si>
+    <t>they</t>
+  </si>
+  <si>
+    <t>crowd people society public group</t>
+  </si>
+  <si>
+    <t>eigentlich</t>
+  </si>
+  <si>
+    <t>eye-gen-tlikh</t>
+  </si>
+  <si>
+    <t>actually/really</t>
+  </si>
+  <si>
+    <t>Was meinst du eigentlich?</t>
+  </si>
+  <si>
+    <t>actually</t>
+  </si>
+  <si>
+    <t>person thinking clarification discussion conversation</t>
+  </si>
+  <si>
+    <t>solch</t>
+  </si>
+  <si>
+    <t>zolkh</t>
+  </si>
+  <si>
+    <t>such</t>
+  </si>
+  <si>
+    <t>Solch ein Tag ist selten.</t>
+  </si>
+  <si>
+    <t>this</t>
+  </si>
+  <si>
+    <t>these</t>
+  </si>
+  <si>
+    <t>unique object example special situation</t>
+  </si>
+  <si>
+    <t>Determiner</t>
+  </si>
+  <si>
+    <t>emotionale</t>
+  </si>
+  <si>
+    <t>e-mo-tsyo-na-le</t>
+  </si>
+  <si>
+    <t>emotional</t>
+  </si>
+  <si>
+    <t>Wir sprechen über emotionale Themen.</t>
+  </si>
+  <si>
+    <t>logical</t>
+  </si>
+  <si>
+    <t>person crying feelings emotional conversation</t>
+  </si>
+  <si>
+    <t>Themen</t>
+  </si>
+  <si>
+    <t>tay-men</t>
+  </si>
+  <si>
+    <t>topics/themes</t>
+  </si>
+  <si>
+    <t>Die Themen sind interessant.</t>
+  </si>
+  <si>
+    <t>topics</t>
+  </si>
+  <si>
+    <t>houses</t>
+  </si>
+  <si>
+    <t>animals</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>classroom discussion subjects learning ideas</t>
+  </si>
+  <si>
+    <t>Scherze</t>
+  </si>
+  <si>
+    <t>sher-tse</t>
+  </si>
+  <si>
+    <t>Seine Scherze sind lustig.</t>
+  </si>
+  <si>
+    <t>answers</t>
+  </si>
+  <si>
+    <t>friends laughing comedy joke humor</t>
+  </si>
+  <si>
+    <t>Oberschule</t>
+  </si>
+  <si>
+    <t>oh-ber-shoo-le</t>
+  </si>
+  <si>
+    <t>secondary school</t>
+  </si>
+  <si>
+    <t>Er geht zur Oberschule.</t>
+  </si>
+  <si>
+    <t>hospital</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>office</t>
+  </si>
+  <si>
+    <t>🏫</t>
+  </si>
+  <si>
+    <t>school building students classroom education</t>
+  </si>
+  <si>
+    <t>nehmen</t>
+  </si>
+  <si>
+    <t>nay-men</t>
+  </si>
+  <si>
+    <t>to take</t>
+  </si>
+  <si>
+    <t>Ich nehme den Stift.</t>
+  </si>
+  <si>
+    <t>give</t>
+  </si>
+  <si>
+    <t>take</t>
+  </si>
+  <si>
+    <t>✋</t>
+  </si>
+  <si>
+    <t>person taking object hand grabbing</t>
+  </si>
+  <si>
+    <t>tatsächlich</t>
+  </si>
+  <si>
+    <t>tat-zekh-likh</t>
+  </si>
+  <si>
+    <t>actually/in fact</t>
+  </si>
+  <si>
+    <t>Das ist tatsächlich wahr.</t>
+  </si>
+  <si>
+    <t>person confirming fact truth evidence</t>
+  </si>
+  <si>
+    <t>dran</t>
+  </si>
+  <si>
+    <t>drahn</t>
+  </si>
+  <si>
+    <t>on it/next turn</t>
+  </si>
+  <si>
+    <t>Du bist jetzt dran.</t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>next turn</t>
+  </si>
+  <si>
+    <t>absent</t>
+  </si>
+  <si>
+    <t>🎯</t>
+  </si>
+  <si>
+    <t>person's turn game participation activity</t>
+  </si>
+  <si>
+    <t>teil</t>
+  </si>
+  <si>
+    <t>tile</t>
+  </si>
+  <si>
+    <t>part</t>
+  </si>
+  <si>
+    <t>Ich nehme daran teil.</t>
+  </si>
+  <si>
+    <t>whole</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>🧩</t>
+  </si>
+  <si>
+    <t>puzzle piece section part component</t>
+  </si>
+  <si>
+    <t>person shaking head negative response disagreement</t>
+  </si>
+  <si>
+    <t>schlimm</t>
+  </si>
+  <si>
+    <t>shlimm</t>
+  </si>
+  <si>
+    <t>bad/terrible</t>
+  </si>
+  <si>
+    <t>Das ist schlimm.</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>😨</t>
+  </si>
+  <si>
+    <t>disaster accident worried person problem</t>
+  </si>
+  <si>
+    <t>allein</t>
+  </si>
+  <si>
+    <t>ah-line</t>
+  </si>
+  <si>
+    <t>alone</t>
+  </si>
+  <si>
+    <t>Ich bin allein zu Hause.</t>
+  </si>
+  <si>
+    <t>together</t>
+  </si>
+  <si>
+    <t>with friends</t>
+  </si>
+  <si>
+    <t>in group</t>
+  </si>
+  <si>
+    <t>🚶</t>
+  </si>
+  <si>
+    <t>person alone empty room solitude</t>
+  </si>
+  <si>
+    <t>Gott</t>
+  </si>
+  <si>
+    <t>got</t>
+  </si>
+  <si>
+    <t>God</t>
+  </si>
+  <si>
+    <t>Gott helfe uns.</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>der</t>
+  </si>
+  <si>
+    <t>🙏</t>
+  </si>
+  <si>
+    <t>religious prayer church spiritual figure</t>
+  </si>
+  <si>
+    <t>dann</t>
+  </si>
+  <si>
+    <t>dan</t>
+  </si>
+  <si>
+    <t>then</t>
+  </si>
+  <si>
+    <t>Dann gehen wir nach Hause.</t>
+  </si>
+  <si>
+    <t>time sequence next step timeline</t>
+  </si>
+  <si>
+    <t>konnte</t>
+  </si>
+  <si>
+    <t>kon-te</t>
+  </si>
+  <si>
+    <t>could</t>
+  </si>
+  <si>
+    <t>Ich konnte nicht kommen.</t>
+  </si>
+  <si>
+    <t>person able to do task past ability</t>
+  </si>
+  <si>
+    <t>Verb (können - past)</t>
+  </si>
+  <si>
+    <t>ganzen</t>
+  </si>
+  <si>
+    <t>gan-tsen</t>
+  </si>
+  <si>
+    <t>whole/entire</t>
+  </si>
+  <si>
+    <t>Den ganzen Tag habe ich gelernt.</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>🌍</t>
+  </si>
+  <si>
+    <t>complete object full day entire thing</t>
+  </si>
+  <si>
+    <t>niemand</t>
+  </si>
+  <si>
+    <t>nee-mand</t>
+  </si>
+  <si>
+    <t>Niemand war dort.</t>
+  </si>
+  <si>
+    <t>🚫</t>
+  </si>
+  <si>
+    <t>empty place no people absence</t>
+  </si>
+  <si>
+    <t>wie</t>
+  </si>
+  <si>
+    <t>vee</t>
+  </si>
+  <si>
+    <t>how/like</t>
+  </si>
+  <si>
+    <t>Wie geht es dir?</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>person asking question conversation curiosity</t>
+  </si>
+  <si>
+    <t>Entscheidung</t>
+  </si>
+  <si>
+    <t>ent-shy-dung</t>
+  </si>
+  <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>Das war eine gute Entscheidung.</t>
+  </si>
+  <si>
+    <t>⚖️</t>
+  </si>
+  <si>
+    <t>person choosing between options decision making</t>
+  </si>
+  <si>
+    <t>kann</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>Er kann Deutsch sprechen.</t>
+  </si>
+  <si>
+    <t>🗣️</t>
+  </si>
+  <si>
+    <t>person showing skill ability talent</t>
+  </si>
+  <si>
+    <t>wünschte</t>
+  </si>
+  <si>
+    <t>vuensh-te</t>
+  </si>
+  <si>
+    <t>wished</t>
+  </si>
+  <si>
+    <t>Ich wünschte mir ein Fahrrad.</t>
+  </si>
+  <si>
+    <t>bought</t>
+  </si>
+  <si>
+    <t>sold</t>
+  </si>
+  <si>
+    <t>found</t>
+  </si>
+  <si>
+    <t>🌠</t>
+  </si>
+  <si>
+    <t>person making wish dream hope</t>
+  </si>
+  <si>
+    <t>wäre</t>
+  </si>
+  <si>
+    <t>va-re</t>
+  </si>
+  <si>
+    <t>would be</t>
+  </si>
+  <si>
+    <t>Das wäre schön.</t>
+  </si>
+  <si>
+    <t>will be</t>
+  </si>
+  <si>
+    <t>✨</t>
+  </si>
+  <si>
+    <t>person imagining future possibility dream</t>
+  </si>
+  <si>
+    <t>Verb (sein - Konjunktiv II)</t>
+  </si>
+  <si>
+    <t>starker</t>
+  </si>
+  <si>
+    <t>shtar-ker</t>
+  </si>
+  <si>
+    <t>strong</t>
+  </si>
+  <si>
+    <t>Er ist ein starker Mann.</t>
+  </si>
+  <si>
+    <t>weak</t>
+  </si>
+  <si>
+    <t>muscular man strength fitness power</t>
+  </si>
+  <si>
+    <t>Charakter</t>
+  </si>
+  <si>
+    <t>ka-rak-ter</t>
+  </si>
+  <si>
+    <t>character/personality</t>
+  </si>
+  <si>
+    <t>Sie hat einen guten Charakter.</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>character</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>🎭</t>
+  </si>
+  <si>
+    <t>person personality traits identity behavior</t>
+  </si>
+  <si>
+    <t>lieb</t>
+  </si>
+  <si>
+    <t>leep</t>
+  </si>
+  <si>
+    <t>kind/dear</t>
+  </si>
+  <si>
+    <t>Sie ist sehr lieb.</t>
+  </si>
+  <si>
+    <t>lazy</t>
+  </si>
+  <si>
+    <t>🥰</t>
+  </si>
+  <si>
+    <t>kind person helping caring friendly</t>
+  </si>
+  <si>
+    <t>two choices contrast discussion argument</t>
+  </si>
+  <si>
+    <t>weiß</t>
+  </si>
+  <si>
+    <t>vice</t>
+  </si>
+  <si>
+    <t>know</t>
+  </si>
+  <si>
+    <t>Ich weiß die Antwort.</t>
+  </si>
+  <si>
+    <t>guess</t>
+  </si>
+  <si>
+    <t>hide</t>
+  </si>
+  <si>
+    <t>🧠</t>
+  </si>
+  <si>
+    <t>person knowing answer knowledge learning</t>
+  </si>
+  <si>
+    <t>Verb (wissen)</t>
+  </si>
+  <si>
+    <t>ob</t>
+  </si>
+  <si>
+    <t>op</t>
+  </si>
+  <si>
+    <t>whether</t>
+  </si>
+  <si>
+    <t>Ich weiß nicht, ob er kommt.</t>
+  </si>
+  <si>
+    <t>🤷</t>
+  </si>
+  <si>
+    <t>person uncertain decision possibility question</t>
+  </si>
+  <si>
+    <t>weg</t>
+  </si>
+  <si>
+    <t>vek</t>
+  </si>
+  <si>
+    <t>away/gone</t>
+  </si>
+  <si>
+    <t>Er ist weg.</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>away</t>
+  </si>
+  <si>
+    <t>inside</t>
+  </si>
+  <si>
+    <t>🏃</t>
+  </si>
+  <si>
+    <t>person leaving walking away distance</t>
+  </si>
+  <si>
+    <t>fürchterlich</t>
+  </si>
+  <si>
+    <t>fuerkh-ter-likh</t>
+  </si>
+  <si>
+    <t>terrible/awful</t>
+  </si>
+  <si>
+    <t>Das Wetter ist fürchterlich.</t>
+  </si>
+  <si>
+    <t>wonderful</t>
+  </si>
+  <si>
+    <t>funny</t>
+  </si>
+  <si>
+    <t>cheap</t>
+  </si>
+  <si>
+    <t>😱</t>
+  </si>
+  <si>
+    <t>storm disaster frightened person terrible situation</t>
+  </si>
+  <si>
+    <t>richtige</t>
+  </si>
+  <si>
+    <t>rikh-ti-ge</t>
+  </si>
+  <si>
+    <t>right/correct</t>
+  </si>
+  <si>
+    <t>Das ist die richtige Antwort.</t>
+  </si>
+  <si>
+    <t>wrong</t>
+  </si>
+  <si>
+    <t>correct</t>
+  </si>
+  <si>
+    <t>student correct answer checkmark success</t>
+  </si>
+  <si>
+    <t>wenn</t>
+  </si>
+  <si>
+    <t>ven</t>
+  </si>
+  <si>
+    <t>if/when</t>
+  </si>
+  <si>
+    <t>Wenn es regnet, bleibe ich zu Hause.</t>
+  </si>
+  <si>
+    <t>🌦️</t>
+  </si>
+  <si>
+    <t>person deciding based on condition weather</t>
+  </si>
+  <si>
+    <t>andere</t>
+  </si>
+  <si>
+    <t>an-de-re</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Die andere Tasche ist größer.</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>last</t>
+  </si>
+  <si>
+    <t>two different people comparison choice</t>
+  </si>
+  <si>
+    <t>denkt</t>
+  </si>
+  <si>
+    <t>thinks</t>
+  </si>
+  <si>
+    <t>Er denkt an seine Familie.</t>
+  </si>
+  <si>
+    <t>person thinking idea brain reflection</t>
+  </si>
+  <si>
+    <t>bewundernswert</t>
+  </si>
+  <si>
+    <t>be-voon-derns-vert</t>
+  </si>
+  <si>
+    <t>admirable</t>
+  </si>
+  <si>
+    <t>Das ist bewundernswert.</t>
+  </si>
+  <si>
+    <t>boring</t>
+  </si>
+  <si>
+    <t>person receiving praise achievement respect</t>
+  </si>
+  <si>
+    <t>bringt</t>
+  </si>
+  <si>
+    <t>brings</t>
+  </si>
+  <si>
+    <t>Er bringt das Buch mit.</t>
+  </si>
+  <si>
+    <t>takes</t>
+  </si>
+  <si>
+    <t>throws</t>
+  </si>
+  <si>
+    <t>loses</t>
+  </si>
+  <si>
+    <t>📦</t>
+  </si>
+  <si>
+    <t>person carrying gift package delivery</t>
+  </si>
+  <si>
+    <t>alles</t>
+  </si>
+  <si>
+    <t>al-les</t>
+  </si>
+  <si>
+    <t>everything</t>
+  </si>
+  <si>
+    <t>Alles ist bereit.</t>
+  </si>
+  <si>
+    <t>nothing</t>
+  </si>
+  <si>
+    <t>something</t>
+  </si>
+  <si>
+    <t>half</t>
+  </si>
+  <si>
+    <t>many objects collection complete set</t>
+  </si>
+  <si>
+    <t>völlig</t>
+  </si>
+  <si>
+    <t>foel-likh</t>
+  </si>
+  <si>
+    <t>completely</t>
+  </si>
+  <si>
+    <t>Das ist völlig richtig.</t>
+  </si>
+  <si>
+    <t>partly</t>
+  </si>
+  <si>
+    <t>💯</t>
+  </si>
+  <si>
+    <t>full completion perfect result total amount</t>
+  </si>
+  <si>
+    <t>sinnlos</t>
+  </si>
+  <si>
+    <t>zin-lohs</t>
+  </si>
+  <si>
+    <t>meaningless</t>
+  </si>
+  <si>
+    <t>pointless</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>person confused useless task wasted effort</t>
+  </si>
+  <si>
+    <t>sollten</t>
+  </si>
+  <si>
+    <t>zoll-ten</t>
+  </si>
+  <si>
+    <t>should (plural/past form)</t>
+  </si>
+  <si>
+    <t>Wir sollten lernen.</t>
+  </si>
+  <si>
+    <t>students studying advice classroom homework</t>
+  </si>
+  <si>
+    <t>für</t>
+  </si>
+  <si>
+    <t>fuer</t>
+  </si>
+  <si>
+    <t>Das Geschenk ist für dich.</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>without</t>
+  </si>
+  <si>
+    <t>🎁</t>
+  </si>
+  <si>
+    <t>gift present giving someone recipient</t>
+  </si>
+  <si>
+    <t>Prüfung</t>
+  </si>
+  <si>
+    <t>proo-fung</t>
+  </si>
+  <si>
+    <t>exam/test</t>
+  </si>
+  <si>
+    <t>Die Prüfung ist morgen.</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>holiday</t>
+  </si>
+  <si>
+    <t>game</t>
+  </si>
+  <si>
+    <t>students taking exam classroom test paper</t>
+  </si>
+  <si>
+    <t>weißt</t>
+  </si>
+  <si>
+    <t>vyst</t>
+  </si>
+  <si>
+    <t>Weißt du die Antwort?</t>
+  </si>
+  <si>
+    <t>student knowing answer raising hand learning</t>
+  </si>
+  <si>
+    <t>vas</t>
+  </si>
+  <si>
+    <t>what</t>
+  </si>
+  <si>
+    <t>Was machst du heute?</t>
+  </si>
+  <si>
+    <t>person asking question curiosity conversation</t>
+  </si>
+  <si>
+    <t>drankommt</t>
+  </si>
+  <si>
+    <t>drahn-kommt</t>
+  </si>
+  <si>
+    <t>will be on the exam</t>
+  </si>
+  <si>
+    <t>Ich weiß nicht, was drankommt.</t>
+  </si>
+  <si>
+    <t>fails</t>
+  </si>
+  <si>
+    <t>arrives</t>
+  </si>
+  <si>
+    <t>leaves</t>
+  </si>
+  <si>
+    <t>exam syllabus topics study guide classroom</t>
+  </si>
+  <si>
+    <t>Englischprüfung</t>
+  </si>
+  <si>
+    <t>eng-lish-proo-fung</t>
+  </si>
+  <si>
+    <t>English exam</t>
+  </si>
+  <si>
+    <t>Die Englischprüfung ist schwer.</t>
+  </si>
+  <si>
+    <t>math exam</t>
+  </si>
+  <si>
+    <t>english exam</t>
+  </si>
+  <si>
+    <t>sports class</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>🇬🇧📝</t>
+  </si>
+  <si>
+    <t>english test classroom students grammar vocabulary</t>
+  </si>
+  <si>
+    <t>Englisch</t>
+  </si>
+  <si>
+    <t>eng-lish</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Ich lerne Englisch.</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>🇬🇧</t>
+  </si>
+  <si>
+    <t>english language british flag student learning</t>
+  </si>
+  <si>
+    <t>Ojemine</t>
+  </si>
+  <si>
+    <t>o-yeh-mee-neh</t>
+  </si>
+  <si>
+    <t>oh dear / oh my</t>
+  </si>
+  <si>
+    <t>Ojemine, das ist schwierig!</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>oh dear</t>
+  </si>
+  <si>
+    <t>thanks</t>
+  </si>
+  <si>
+    <t>goodbye</t>
+  </si>
+  <si>
+    <t>interjection</t>
+  </si>
+  <si>
+    <t>surprised person shocked reaction unexpected event</t>
+  </si>
+  <si>
+    <t>Interjection</t>
+  </si>
+  <si>
+    <t>Klassenraum</t>
+  </si>
+  <si>
+    <t>klas-sen-rowm</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>Der Klassenraum ist groß.</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>classroom students desks teacher school</t>
+  </si>
+  <si>
+    <t>frühen</t>
+  </si>
+  <si>
+    <t>froo-en</t>
+  </si>
+  <si>
+    <t>early (inflected form)</t>
+  </si>
+  <si>
+    <t>In den frühen Morgenstunden.</t>
+  </si>
+  <si>
+    <t>early</t>
+  </si>
+  <si>
+    <t>🌅</t>
+  </si>
+  <si>
+    <t>sunrise morning dawn early day</t>
   </si>
 </sst>
 </file>
@@ -58,10 +2668,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -79,6 +2689,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -88,7 +2712,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -96,12 +2720,58 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -118,16 +2788,24 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,82 +2818,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -238,31 +2848,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,7 +2878,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,13 +2908,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,13 +2950,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -334,91 +3022,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,26 +3072,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,21 +3111,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -530,8 +3125,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -539,156 +3149,156 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1043,10 +3653,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="12" width="20" customWidth="1"/>
+    <col min="1" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="39.2" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1087,6 +3699,4183 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" t="s">
+        <v>117</v>
+      </c>
+      <c r="L12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
+        <v>124</v>
+      </c>
+      <c r="K13" t="s">
+        <v>125</v>
+      </c>
+      <c r="L13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" t="s">
+        <v>133</v>
+      </c>
+      <c r="K14" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K15" t="s">
+        <v>144</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s">
+        <v>149</v>
+      </c>
+      <c r="G16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H16" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" t="s">
+        <v>153</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" t="s">
+        <v>162</v>
+      </c>
+      <c r="L17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" t="s">
+        <v>172</v>
+      </c>
+      <c r="K18" t="s">
+        <v>173</v>
+      </c>
+      <c r="L18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G19" t="s">
+        <v>180</v>
+      </c>
+      <c r="H19" t="s">
+        <v>181</v>
+      </c>
+      <c r="I19" t="s">
+        <v>115</v>
+      </c>
+      <c r="J19" t="s">
+        <v>182</v>
+      </c>
+      <c r="K19" t="s">
+        <v>183</v>
+      </c>
+      <c r="L19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F20" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
+        <v>191</v>
+      </c>
+      <c r="K20" t="s">
+        <v>192</v>
+      </c>
+      <c r="L20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" t="s">
+        <v>198</v>
+      </c>
+      <c r="G21" t="s">
+        <v>199</v>
+      </c>
+      <c r="H21" t="s">
+        <v>200</v>
+      </c>
+      <c r="I21" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" t="s">
+        <v>202</v>
+      </c>
+      <c r="L21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>203</v>
+      </c>
+      <c r="B22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G22" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" t="s">
+        <v>116</v>
+      </c>
+      <c r="K22" t="s">
+        <v>206</v>
+      </c>
+      <c r="L22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>207</v>
+      </c>
+      <c r="B23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" t="s">
+        <v>209</v>
+      </c>
+      <c r="D23" t="s">
+        <v>210</v>
+      </c>
+      <c r="E23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F23" t="s">
+        <v>209</v>
+      </c>
+      <c r="G23" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" t="s">
+        <v>181</v>
+      </c>
+      <c r="I23" t="s">
+        <v>212</v>
+      </c>
+      <c r="J23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K23" t="s">
+        <v>214</v>
+      </c>
+      <c r="L23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" t="s">
+        <v>221</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" t="s">
+        <v>222</v>
+      </c>
+      <c r="K24" t="s">
+        <v>223</v>
+      </c>
+      <c r="L24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" t="s">
+        <v>230</v>
+      </c>
+      <c r="H25" t="s">
+        <v>231</v>
+      </c>
+      <c r="I25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" t="s">
+        <v>232</v>
+      </c>
+      <c r="K25" t="s">
+        <v>233</v>
+      </c>
+      <c r="L25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>238</v>
+      </c>
+      <c r="G26" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" t="s">
+        <v>240</v>
+      </c>
+      <c r="K26" t="s">
+        <v>241</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" t="s">
+        <v>248</v>
+      </c>
+      <c r="H27" t="s">
+        <v>249</v>
+      </c>
+      <c r="I27" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" t="s">
+        <v>250</v>
+      </c>
+      <c r="K27" t="s">
+        <v>251</v>
+      </c>
+      <c r="L27" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" t="s">
+        <v>254</v>
+      </c>
+      <c r="C28" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" t="s">
+        <v>261</v>
+      </c>
+      <c r="K28" t="s">
+        <v>262</v>
+      </c>
+      <c r="L28" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" t="s">
+        <v>267</v>
+      </c>
+      <c r="F29" t="s">
+        <v>265</v>
+      </c>
+      <c r="G29" t="s">
+        <v>268</v>
+      </c>
+      <c r="H29" t="s">
+        <v>269</v>
+      </c>
+      <c r="I29" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29" t="s">
+        <v>270</v>
+      </c>
+      <c r="K29" t="s">
+        <v>271</v>
+      </c>
+      <c r="L29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>272</v>
+      </c>
+      <c r="B30" t="s">
+        <v>273</v>
+      </c>
+      <c r="C30" t="s">
+        <v>274</v>
+      </c>
+      <c r="D30" t="s">
+        <v>275</v>
+      </c>
+      <c r="E30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" t="s">
+        <v>274</v>
+      </c>
+      <c r="G30" t="s">
+        <v>277</v>
+      </c>
+      <c r="H30" t="s">
+        <v>278</v>
+      </c>
+      <c r="I30" t="s">
+        <v>279</v>
+      </c>
+      <c r="J30" t="s">
+        <v>280</v>
+      </c>
+      <c r="K30" t="s">
+        <v>281</v>
+      </c>
+      <c r="L30" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>283</v>
+      </c>
+      <c r="B31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C31" t="s">
+        <v>285</v>
+      </c>
+      <c r="D31" t="s">
+        <v>286</v>
+      </c>
+      <c r="E31" t="s">
+        <v>287</v>
+      </c>
+      <c r="F31" t="s">
+        <v>288</v>
+      </c>
+      <c r="G31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H31" t="s">
+        <v>289</v>
+      </c>
+      <c r="I31" t="s">
+        <v>171</v>
+      </c>
+      <c r="J31" t="s">
+        <v>290</v>
+      </c>
+      <c r="K31" t="s">
+        <v>291</v>
+      </c>
+      <c r="L31" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" t="s">
+        <v>293</v>
+      </c>
+      <c r="B32" t="s">
+        <v>294</v>
+      </c>
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" t="s">
+        <v>295</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" t="s">
+        <v>296</v>
+      </c>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" t="s">
+        <v>297</v>
+      </c>
+      <c r="K32" t="s">
+        <v>298</v>
+      </c>
+      <c r="L32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>299</v>
+      </c>
+      <c r="B33" t="s">
+        <v>300</v>
+      </c>
+      <c r="C33" t="s">
+        <v>301</v>
+      </c>
+      <c r="D33" t="s">
+        <v>302</v>
+      </c>
+      <c r="E33" t="s">
+        <v>303</v>
+      </c>
+      <c r="F33" t="s">
+        <v>304</v>
+      </c>
+      <c r="G33" t="s">
+        <v>301</v>
+      </c>
+      <c r="H33" t="s">
+        <v>305</v>
+      </c>
+      <c r="I33" t="s">
+        <v>306</v>
+      </c>
+      <c r="J33" t="s">
+        <v>307</v>
+      </c>
+      <c r="K33" t="s">
+        <v>308</v>
+      </c>
+      <c r="L33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" t="s">
+        <v>267</v>
+      </c>
+      <c r="G34" t="s">
+        <v>312</v>
+      </c>
+      <c r="H34" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" t="s">
+        <v>115</v>
+      </c>
+      <c r="J34" t="s">
+        <v>314</v>
+      </c>
+      <c r="K34" t="s">
+        <v>315</v>
+      </c>
+      <c r="L34" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>317</v>
+      </c>
+      <c r="B35" t="s">
+        <v>318</v>
+      </c>
+      <c r="C35" t="s">
+        <v>319</v>
+      </c>
+      <c r="D35" t="s">
+        <v>320</v>
+      </c>
+      <c r="E35" t="s">
+        <v>321</v>
+      </c>
+      <c r="F35" t="s">
+        <v>319</v>
+      </c>
+      <c r="G35" t="s">
+        <v>322</v>
+      </c>
+      <c r="H35" t="s">
+        <v>323</v>
+      </c>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" t="s">
+        <v>324</v>
+      </c>
+      <c r="K35" t="s">
+        <v>325</v>
+      </c>
+      <c r="L35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>326</v>
+      </c>
+      <c r="B36" t="s">
+        <v>327</v>
+      </c>
+      <c r="C36" t="s">
+        <v>328</v>
+      </c>
+      <c r="D36" t="s">
+        <v>329</v>
+      </c>
+      <c r="E36" t="s">
+        <v>330</v>
+      </c>
+      <c r="F36" t="s">
+        <v>331</v>
+      </c>
+      <c r="G36" t="s">
+        <v>332</v>
+      </c>
+      <c r="H36" t="s">
+        <v>333</v>
+      </c>
+      <c r="I36" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" t="s">
+        <v>334</v>
+      </c>
+      <c r="K36" t="s">
+        <v>335</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>336</v>
+      </c>
+      <c r="B37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>339</v>
+      </c>
+      <c r="E37" t="s">
+        <v>340</v>
+      </c>
+      <c r="F37" t="s">
+        <v>338</v>
+      </c>
+      <c r="G37" t="s">
+        <v>341</v>
+      </c>
+      <c r="H37" t="s">
+        <v>342</v>
+      </c>
+      <c r="I37" t="s">
+        <v>115</v>
+      </c>
+      <c r="J37" t="s">
+        <v>343</v>
+      </c>
+      <c r="K37" t="s">
+        <v>344</v>
+      </c>
+      <c r="L37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>345</v>
+      </c>
+      <c r="B38" t="s">
+        <v>346</v>
+      </c>
+      <c r="C38" t="s">
+        <v>347</v>
+      </c>
+      <c r="D38" t="s">
+        <v>348</v>
+      </c>
+      <c r="E38" t="s">
+        <v>349</v>
+      </c>
+      <c r="F38" t="s">
+        <v>347</v>
+      </c>
+      <c r="G38" t="s">
+        <v>160</v>
+      </c>
+      <c r="H38" t="s">
+        <v>350</v>
+      </c>
+      <c r="I38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s">
+        <v>133</v>
+      </c>
+      <c r="K38" t="s">
+        <v>351</v>
+      </c>
+      <c r="L38" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>353</v>
+      </c>
+      <c r="B39" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" t="s">
+        <v>355</v>
+      </c>
+      <c r="D39" t="s">
+        <v>356</v>
+      </c>
+      <c r="E39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" t="s">
+        <v>355</v>
+      </c>
+      <c r="G39" t="s">
+        <v>358</v>
+      </c>
+      <c r="H39" t="s">
+        <v>359</v>
+      </c>
+      <c r="I39" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" t="s">
+        <v>360</v>
+      </c>
+      <c r="K39" t="s">
+        <v>361</v>
+      </c>
+      <c r="L39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>362</v>
+      </c>
+      <c r="B40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" t="s">
+        <v>364</v>
+      </c>
+      <c r="E40" t="s">
+        <v>278</v>
+      </c>
+      <c r="F40" t="s">
+        <v>274</v>
+      </c>
+      <c r="G40" t="s">
+        <v>277</v>
+      </c>
+      <c r="H40" t="s">
+        <v>365</v>
+      </c>
+      <c r="I40" t="s">
+        <v>279</v>
+      </c>
+      <c r="J40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K40" t="s">
+        <v>366</v>
+      </c>
+      <c r="L40" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>367</v>
+      </c>
+      <c r="B41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" t="s">
+        <v>369</v>
+      </c>
+      <c r="E41" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H41" t="s">
+        <v>370</v>
+      </c>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" t="s">
+        <v>371</v>
+      </c>
+      <c r="K41" t="s">
+        <v>372</v>
+      </c>
+      <c r="L41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" t="s">
+        <v>376</v>
+      </c>
+      <c r="D42" t="s">
+        <v>377</v>
+      </c>
+      <c r="E42" t="s">
+        <v>378</v>
+      </c>
+      <c r="F42" t="s">
+        <v>376</v>
+      </c>
+      <c r="G42" t="s">
+        <v>221</v>
+      </c>
+      <c r="H42" t="s">
+        <v>248</v>
+      </c>
+      <c r="I42" t="s">
+        <v>59</v>
+      </c>
+      <c r="J42" t="s">
+        <v>379</v>
+      </c>
+      <c r="K42" t="s">
+        <v>380</v>
+      </c>
+      <c r="L42" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>381</v>
+      </c>
+      <c r="B43" t="s">
+        <v>382</v>
+      </c>
+      <c r="C43" t="s">
+        <v>383</v>
+      </c>
+      <c r="D43" t="s">
+        <v>384</v>
+      </c>
+      <c r="E43" t="s">
+        <v>385</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" t="s">
+        <v>386</v>
+      </c>
+      <c r="K43" t="s">
+        <v>387</v>
+      </c>
+      <c r="L43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>388</v>
+      </c>
+      <c r="B44" t="s">
+        <v>389</v>
+      </c>
+      <c r="C44" t="s">
+        <v>390</v>
+      </c>
+      <c r="D44" t="s">
+        <v>391</v>
+      </c>
+      <c r="E44" t="s">
+        <v>392</v>
+      </c>
+      <c r="F44" t="s">
+        <v>289</v>
+      </c>
+      <c r="G44" t="s">
+        <v>390</v>
+      </c>
+      <c r="H44" t="s">
+        <v>393</v>
+      </c>
+      <c r="I44" t="s">
+        <v>171</v>
+      </c>
+      <c r="J44" t="s">
+        <v>394</v>
+      </c>
+      <c r="K44" t="s">
+        <v>395</v>
+      </c>
+      <c r="L44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>396</v>
+      </c>
+      <c r="B45" t="s">
+        <v>397</v>
+      </c>
+      <c r="C45" t="s">
+        <v>398</v>
+      </c>
+      <c r="D45" t="s">
+        <v>399</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>398</v>
+      </c>
+      <c r="G45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" t="s">
+        <v>400</v>
+      </c>
+      <c r="K45" t="s">
+        <v>401</v>
+      </c>
+      <c r="L45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>402</v>
+      </c>
+      <c r="B46" t="s">
+        <v>403</v>
+      </c>
+      <c r="C46" t="s">
+        <v>404</v>
+      </c>
+      <c r="D46" t="s">
+        <v>405</v>
+      </c>
+      <c r="E46" t="s">
+        <v>406</v>
+      </c>
+      <c r="F46" t="s">
+        <v>404</v>
+      </c>
+      <c r="G46" t="s">
+        <v>260</v>
+      </c>
+      <c r="H46" t="s">
+        <v>407</v>
+      </c>
+      <c r="I46" t="s">
+        <v>171</v>
+      </c>
+      <c r="J46" t="s">
+        <v>408</v>
+      </c>
+      <c r="K46" t="s">
+        <v>409</v>
+      </c>
+      <c r="L46" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" t="s">
+        <v>410</v>
+      </c>
+      <c r="B47" t="s">
+        <v>411</v>
+      </c>
+      <c r="C47" t="s">
+        <v>412</v>
+      </c>
+      <c r="D47" t="s">
+        <v>413</v>
+      </c>
+      <c r="E47" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" t="s">
+        <v>414</v>
+      </c>
+      <c r="G47" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" t="s">
+        <v>44</v>
+      </c>
+      <c r="I47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J47" t="s">
+        <v>415</v>
+      </c>
+      <c r="K47" t="s">
+        <v>416</v>
+      </c>
+      <c r="L47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" t="s">
+        <v>417</v>
+      </c>
+      <c r="B48" t="s">
+        <v>418</v>
+      </c>
+      <c r="C48" t="s">
+        <v>419</v>
+      </c>
+      <c r="D48" t="s">
+        <v>420</v>
+      </c>
+      <c r="E48" t="s">
+        <v>419</v>
+      </c>
+      <c r="F48" t="s">
+        <v>421</v>
+      </c>
+      <c r="G48" t="s">
+        <v>422</v>
+      </c>
+      <c r="H48" t="s">
+        <v>423</v>
+      </c>
+      <c r="I48" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" t="s">
+        <v>424</v>
+      </c>
+      <c r="K48" t="s">
+        <v>425</v>
+      </c>
+      <c r="L48" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>427</v>
+      </c>
+      <c r="B49" t="s">
+        <v>428</v>
+      </c>
+      <c r="C49" t="s">
+        <v>429</v>
+      </c>
+      <c r="D49" t="s">
+        <v>430</v>
+      </c>
+      <c r="E49" t="s">
+        <v>431</v>
+      </c>
+      <c r="F49" t="s">
+        <v>432</v>
+      </c>
+      <c r="G49" t="s">
+        <v>433</v>
+      </c>
+      <c r="H49" t="s">
+        <v>179</v>
+      </c>
+      <c r="I49" t="s">
+        <v>59</v>
+      </c>
+      <c r="J49" t="s">
+        <v>434</v>
+      </c>
+      <c r="K49" t="s">
+        <v>435</v>
+      </c>
+      <c r="L49" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>437</v>
+      </c>
+      <c r="B50" t="s">
+        <v>438</v>
+      </c>
+      <c r="C50" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" t="s">
+        <v>439</v>
+      </c>
+      <c r="E50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F50" t="s">
+        <v>268</v>
+      </c>
+      <c r="G50" t="s">
+        <v>267</v>
+      </c>
+      <c r="H50" t="s">
+        <v>440</v>
+      </c>
+      <c r="I50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J50" t="s">
+        <v>441</v>
+      </c>
+      <c r="K50" t="s">
+        <v>442</v>
+      </c>
+      <c r="L50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" t="s">
+        <v>443</v>
+      </c>
+      <c r="B51" t="s">
+        <v>444</v>
+      </c>
+      <c r="C51" t="s">
+        <v>445</v>
+      </c>
+      <c r="D51" t="s">
+        <v>446</v>
+      </c>
+      <c r="E51" t="s">
+        <v>447</v>
+      </c>
+      <c r="F51" t="s">
+        <v>448</v>
+      </c>
+      <c r="G51" t="s">
+        <v>445</v>
+      </c>
+      <c r="H51" t="s">
+        <v>449</v>
+      </c>
+      <c r="I51" t="s">
+        <v>171</v>
+      </c>
+      <c r="J51" t="s">
+        <v>450</v>
+      </c>
+      <c r="K51" t="s">
+        <v>451</v>
+      </c>
+      <c r="L51" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
+        <v>453</v>
+      </c>
+      <c r="B52" t="s">
+        <v>454</v>
+      </c>
+      <c r="C52" t="s">
+        <v>455</v>
+      </c>
+      <c r="D52" t="s">
+        <v>456</v>
+      </c>
+      <c r="E52" t="s">
+        <v>457</v>
+      </c>
+      <c r="F52" t="s">
+        <v>458</v>
+      </c>
+      <c r="G52" t="s">
+        <v>459</v>
+      </c>
+      <c r="H52" t="s">
+        <v>460</v>
+      </c>
+      <c r="I52" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" t="s">
+        <v>461</v>
+      </c>
+      <c r="L52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
+        <v>462</v>
+      </c>
+      <c r="B53" t="s">
+        <v>463</v>
+      </c>
+      <c r="C53" t="s">
+        <v>464</v>
+      </c>
+      <c r="D53" t="s">
+        <v>465</v>
+      </c>
+      <c r="E53" t="s">
+        <v>466</v>
+      </c>
+      <c r="F53" t="s">
+        <v>464</v>
+      </c>
+      <c r="G53" t="s">
+        <v>440</v>
+      </c>
+      <c r="H53" t="s">
+        <v>112</v>
+      </c>
+      <c r="I53" t="s">
+        <v>115</v>
+      </c>
+      <c r="J53" t="s">
+        <v>96</v>
+      </c>
+      <c r="K53" t="s">
+        <v>467</v>
+      </c>
+      <c r="L53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" t="s">
+        <v>468</v>
+      </c>
+      <c r="B54" t="s">
+        <v>469</v>
+      </c>
+      <c r="C54" t="s">
+        <v>470</v>
+      </c>
+      <c r="D54" t="s">
+        <v>471</v>
+      </c>
+      <c r="E54" t="s">
+        <v>472</v>
+      </c>
+      <c r="F54" t="s">
+        <v>473</v>
+      </c>
+      <c r="G54" t="s">
+        <v>470</v>
+      </c>
+      <c r="H54" t="s">
+        <v>474</v>
+      </c>
+      <c r="I54" t="s">
+        <v>59</v>
+      </c>
+      <c r="J54" t="s">
+        <v>475</v>
+      </c>
+      <c r="K54" t="s">
+        <v>476</v>
+      </c>
+      <c r="L54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" t="s">
+        <v>477</v>
+      </c>
+      <c r="B55" t="s">
+        <v>478</v>
+      </c>
+      <c r="C55" t="s">
+        <v>479</v>
+      </c>
+      <c r="D55" t="s">
+        <v>480</v>
+      </c>
+      <c r="E55" t="s">
+        <v>260</v>
+      </c>
+      <c r="F55" t="s">
+        <v>481</v>
+      </c>
+      <c r="G55" t="s">
+        <v>407</v>
+      </c>
+      <c r="H55" t="s">
+        <v>289</v>
+      </c>
+      <c r="I55" t="s">
+        <v>482</v>
+      </c>
+      <c r="J55" t="s">
+        <v>483</v>
+      </c>
+      <c r="K55" t="s">
+        <v>484</v>
+      </c>
+      <c r="L55" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" t="s">
+        <v>486</v>
+      </c>
+      <c r="B56" t="s">
+        <v>487</v>
+      </c>
+      <c r="C56" t="s">
+        <v>488</v>
+      </c>
+      <c r="D56" t="s">
+        <v>489</v>
+      </c>
+      <c r="E56" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" t="s">
+        <v>490</v>
+      </c>
+      <c r="G56" t="s">
+        <v>274</v>
+      </c>
+      <c r="H56" t="s">
+        <v>45</v>
+      </c>
+      <c r="I56" t="s">
+        <v>115</v>
+      </c>
+      <c r="J56" t="s">
+        <v>491</v>
+      </c>
+      <c r="K56" t="s">
+        <v>492</v>
+      </c>
+      <c r="L56" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>493</v>
+      </c>
+      <c r="B57" t="s">
+        <v>494</v>
+      </c>
+      <c r="C57" t="s">
+        <v>495</v>
+      </c>
+      <c r="D57" t="s">
+        <v>496</v>
+      </c>
+      <c r="E57" t="s">
+        <v>459</v>
+      </c>
+      <c r="F57" t="s">
+        <v>495</v>
+      </c>
+      <c r="G57" t="s">
+        <v>142</v>
+      </c>
+      <c r="H57" t="s">
+        <v>460</v>
+      </c>
+      <c r="I57" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" t="s">
+        <v>60</v>
+      </c>
+      <c r="K57" t="s">
+        <v>497</v>
+      </c>
+      <c r="L57" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" t="s">
+        <v>499</v>
+      </c>
+      <c r="B58" t="s">
+        <v>500</v>
+      </c>
+      <c r="C58" t="s">
+        <v>501</v>
+      </c>
+      <c r="D58" t="s">
+        <v>502</v>
+      </c>
+      <c r="E58" t="s">
+        <v>503</v>
+      </c>
+      <c r="F58" t="s">
+        <v>501</v>
+      </c>
+      <c r="G58" t="s">
+        <v>504</v>
+      </c>
+      <c r="H58" t="s">
+        <v>505</v>
+      </c>
+      <c r="I58" t="s">
+        <v>506</v>
+      </c>
+      <c r="J58" t="s">
+        <v>507</v>
+      </c>
+      <c r="K58" t="s">
+        <v>508</v>
+      </c>
+      <c r="L58" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>510</v>
+      </c>
+      <c r="B59" t="s">
+        <v>511</v>
+      </c>
+      <c r="C59" t="s">
+        <v>512</v>
+      </c>
+      <c r="D59" t="s">
+        <v>513</v>
+      </c>
+      <c r="E59" t="s">
+        <v>514</v>
+      </c>
+      <c r="F59" t="s">
+        <v>512</v>
+      </c>
+      <c r="G59" t="s">
+        <v>515</v>
+      </c>
+      <c r="H59" t="s">
+        <v>516</v>
+      </c>
+      <c r="I59" t="s">
+        <v>115</v>
+      </c>
+      <c r="J59" t="s">
+        <v>517</v>
+      </c>
+      <c r="K59" t="s">
+        <v>518</v>
+      </c>
+      <c r="L59" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" t="s">
+        <v>520</v>
+      </c>
+      <c r="B60" t="s">
+        <v>521</v>
+      </c>
+      <c r="C60" t="s">
+        <v>522</v>
+      </c>
+      <c r="D60" t="s">
+        <v>523</v>
+      </c>
+      <c r="E60" t="s">
+        <v>524</v>
+      </c>
+      <c r="F60" t="s">
+        <v>525</v>
+      </c>
+      <c r="G60" t="s">
+        <v>522</v>
+      </c>
+      <c r="H60" t="s">
+        <v>526</v>
+      </c>
+      <c r="I60" t="s">
+        <v>306</v>
+      </c>
+      <c r="J60" t="s">
+        <v>434</v>
+      </c>
+      <c r="K60" t="s">
+        <v>527</v>
+      </c>
+      <c r="L60" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" t="s">
+        <v>528</v>
+      </c>
+      <c r="B61" t="s">
+        <v>529</v>
+      </c>
+      <c r="C61" t="s">
+        <v>530</v>
+      </c>
+      <c r="D61" t="s">
+        <v>531</v>
+      </c>
+      <c r="E61" t="s">
+        <v>466</v>
+      </c>
+      <c r="F61" t="s">
+        <v>532</v>
+      </c>
+      <c r="G61" t="s">
+        <v>112</v>
+      </c>
+      <c r="H61" t="s">
+        <v>45</v>
+      </c>
+      <c r="I61" t="s">
+        <v>115</v>
+      </c>
+      <c r="J61" t="s">
+        <v>38</v>
+      </c>
+      <c r="K61" t="s">
+        <v>533</v>
+      </c>
+      <c r="L61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
+        <v>534</v>
+      </c>
+      <c r="B62" t="s">
+        <v>535</v>
+      </c>
+      <c r="C62" t="s">
+        <v>536</v>
+      </c>
+      <c r="D62" t="s">
+        <v>537</v>
+      </c>
+      <c r="E62" t="s">
+        <v>538</v>
+      </c>
+      <c r="F62" t="s">
+        <v>211</v>
+      </c>
+      <c r="G62" t="s">
+        <v>536</v>
+      </c>
+      <c r="H62" t="s">
+        <v>539</v>
+      </c>
+      <c r="I62" t="s">
+        <v>212</v>
+      </c>
+      <c r="J62" t="s">
+        <v>213</v>
+      </c>
+      <c r="K62" t="s">
+        <v>540</v>
+      </c>
+      <c r="L62" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" t="s">
+        <v>542</v>
+      </c>
+      <c r="B63" t="s">
+        <v>543</v>
+      </c>
+      <c r="C63" t="s">
+        <v>544</v>
+      </c>
+      <c r="D63" t="s">
+        <v>545</v>
+      </c>
+      <c r="E63" t="s">
+        <v>546</v>
+      </c>
+      <c r="F63" t="s">
+        <v>544</v>
+      </c>
+      <c r="G63" t="s">
+        <v>248</v>
+      </c>
+      <c r="H63" t="s">
+        <v>58</v>
+      </c>
+      <c r="I63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J63" t="s">
+        <v>475</v>
+      </c>
+      <c r="K63" t="s">
+        <v>547</v>
+      </c>
+      <c r="L63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" t="s">
+        <v>548</v>
+      </c>
+      <c r="B64" t="s">
+        <v>549</v>
+      </c>
+      <c r="C64" t="s">
+        <v>550</v>
+      </c>
+      <c r="D64" t="s">
+        <v>551</v>
+      </c>
+      <c r="E64" t="s">
+        <v>448</v>
+      </c>
+      <c r="F64" t="s">
+        <v>552</v>
+      </c>
+      <c r="G64" t="s">
+        <v>553</v>
+      </c>
+      <c r="H64" t="s">
+        <v>554</v>
+      </c>
+      <c r="I64" t="s">
+        <v>555</v>
+      </c>
+      <c r="J64" t="s">
+        <v>161</v>
+      </c>
+      <c r="K64" t="s">
+        <v>556</v>
+      </c>
+      <c r="L64" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
+        <v>557</v>
+      </c>
+      <c r="B65" t="s">
+        <v>558</v>
+      </c>
+      <c r="C65" t="s">
+        <v>445</v>
+      </c>
+      <c r="D65" t="s">
+        <v>559</v>
+      </c>
+      <c r="E65" t="s">
+        <v>449</v>
+      </c>
+      <c r="F65" t="s">
+        <v>445</v>
+      </c>
+      <c r="G65" t="s">
+        <v>447</v>
+      </c>
+      <c r="H65" t="s">
+        <v>560</v>
+      </c>
+      <c r="I65" t="s">
+        <v>555</v>
+      </c>
+      <c r="J65" t="s">
+        <v>408</v>
+      </c>
+      <c r="K65" t="s">
+        <v>561</v>
+      </c>
+      <c r="L65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" t="s">
+        <v>562</v>
+      </c>
+      <c r="B66" t="s">
+        <v>563</v>
+      </c>
+      <c r="C66" t="s">
+        <v>564</v>
+      </c>
+      <c r="D66" t="s">
+        <v>565</v>
+      </c>
+      <c r="E66" t="s">
+        <v>566</v>
+      </c>
+      <c r="F66" t="s">
+        <v>567</v>
+      </c>
+      <c r="G66" t="s">
+        <v>568</v>
+      </c>
+      <c r="H66" t="s">
+        <v>569</v>
+      </c>
+      <c r="I66" t="s">
+        <v>555</v>
+      </c>
+      <c r="J66" t="s">
+        <v>570</v>
+      </c>
+      <c r="K66" t="s">
+        <v>571</v>
+      </c>
+      <c r="L66" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" t="s">
+        <v>572</v>
+      </c>
+      <c r="B67" t="s">
+        <v>573</v>
+      </c>
+      <c r="C67" t="s">
+        <v>574</v>
+      </c>
+      <c r="D67" t="s">
+        <v>575</v>
+      </c>
+      <c r="E67" t="s">
+        <v>576</v>
+      </c>
+      <c r="F67" t="s">
+        <v>577</v>
+      </c>
+      <c r="G67" t="s">
+        <v>322</v>
+      </c>
+      <c r="H67" t="s">
+        <v>460</v>
+      </c>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s">
+        <v>578</v>
+      </c>
+      <c r="K67" t="s">
+        <v>579</v>
+      </c>
+      <c r="L67" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" t="s">
+        <v>580</v>
+      </c>
+      <c r="B68" t="s">
+        <v>581</v>
+      </c>
+      <c r="C68" t="s">
+        <v>582</v>
+      </c>
+      <c r="D68" t="s">
+        <v>583</v>
+      </c>
+      <c r="E68" t="s">
+        <v>466</v>
+      </c>
+      <c r="F68" t="s">
+        <v>532</v>
+      </c>
+      <c r="G68" t="s">
+        <v>112</v>
+      </c>
+      <c r="H68" t="s">
+        <v>113</v>
+      </c>
+      <c r="I68" t="s">
+        <v>115</v>
+      </c>
+      <c r="J68" t="s">
+        <v>96</v>
+      </c>
+      <c r="K68" t="s">
+        <v>584</v>
+      </c>
+      <c r="L68" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" t="s">
+        <v>585</v>
+      </c>
+      <c r="B69" t="s">
+        <v>586</v>
+      </c>
+      <c r="C69" t="s">
+        <v>587</v>
+      </c>
+      <c r="D69" t="s">
+        <v>588</v>
+      </c>
+      <c r="E69" t="s">
+        <v>589</v>
+      </c>
+      <c r="F69" t="s">
+        <v>590</v>
+      </c>
+      <c r="G69" t="s">
+        <v>591</v>
+      </c>
+      <c r="H69" t="s">
+        <v>249</v>
+      </c>
+      <c r="I69" t="s">
+        <v>115</v>
+      </c>
+      <c r="J69" t="s">
+        <v>592</v>
+      </c>
+      <c r="K69" t="s">
+        <v>593</v>
+      </c>
+      <c r="L69" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" t="s">
+        <v>594</v>
+      </c>
+      <c r="B70" t="s">
+        <v>595</v>
+      </c>
+      <c r="C70" t="s">
+        <v>596</v>
+      </c>
+      <c r="D70" t="s">
+        <v>597</v>
+      </c>
+      <c r="E70" t="s">
+        <v>598</v>
+      </c>
+      <c r="F70" t="s">
+        <v>596</v>
+      </c>
+      <c r="G70" t="s">
+        <v>599</v>
+      </c>
+      <c r="H70" t="s">
+        <v>600</v>
+      </c>
+      <c r="I70" t="s">
+        <v>482</v>
+      </c>
+      <c r="J70" t="s">
+        <v>601</v>
+      </c>
+      <c r="K70" t="s">
+        <v>602</v>
+      </c>
+      <c r="L70" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" t="s">
+        <v>264</v>
+      </c>
+      <c r="C71" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" t="s">
+        <v>266</v>
+      </c>
+      <c r="E71" t="s">
+        <v>267</v>
+      </c>
+      <c r="F71" t="s">
+        <v>265</v>
+      </c>
+      <c r="G71" t="s">
+        <v>268</v>
+      </c>
+      <c r="H71" t="s">
+        <v>269</v>
+      </c>
+      <c r="I71" t="s">
+        <v>115</v>
+      </c>
+      <c r="J71" t="s">
+        <v>270</v>
+      </c>
+      <c r="K71" t="s">
+        <v>603</v>
+      </c>
+      <c r="L71" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" t="s">
+        <v>604</v>
+      </c>
+      <c r="B72" t="s">
+        <v>605</v>
+      </c>
+      <c r="C72" t="s">
+        <v>606</v>
+      </c>
+      <c r="D72" t="s">
+        <v>607</v>
+      </c>
+      <c r="E72" t="s">
+        <v>608</v>
+      </c>
+      <c r="F72" t="s">
+        <v>220</v>
+      </c>
+      <c r="G72" t="s">
+        <v>248</v>
+      </c>
+      <c r="H72" t="s">
+        <v>95</v>
+      </c>
+      <c r="I72" t="s">
+        <v>59</v>
+      </c>
+      <c r="J72" t="s">
+        <v>609</v>
+      </c>
+      <c r="K72" t="s">
+        <v>610</v>
+      </c>
+      <c r="L72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>611</v>
+      </c>
+      <c r="B73" t="s">
+        <v>612</v>
+      </c>
+      <c r="C73" t="s">
+        <v>613</v>
+      </c>
+      <c r="D73" t="s">
+        <v>614</v>
+      </c>
+      <c r="E73" t="s">
+        <v>615</v>
+      </c>
+      <c r="F73" t="s">
+        <v>613</v>
+      </c>
+      <c r="G73" t="s">
+        <v>616</v>
+      </c>
+      <c r="H73" t="s">
+        <v>617</v>
+      </c>
+      <c r="I73" t="s">
+        <v>59</v>
+      </c>
+      <c r="J73" t="s">
+        <v>618</v>
+      </c>
+      <c r="K73" t="s">
+        <v>619</v>
+      </c>
+      <c r="L73" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" t="s">
+        <v>620</v>
+      </c>
+      <c r="B74" t="s">
+        <v>621</v>
+      </c>
+      <c r="C74" t="s">
+        <v>622</v>
+      </c>
+      <c r="D74" t="s">
+        <v>623</v>
+      </c>
+      <c r="E74" t="s">
+        <v>289</v>
+      </c>
+      <c r="F74" t="s">
+        <v>622</v>
+      </c>
+      <c r="G74" t="s">
+        <v>393</v>
+      </c>
+      <c r="H74" t="s">
+        <v>624</v>
+      </c>
+      <c r="I74" t="s">
+        <v>625</v>
+      </c>
+      <c r="J74" t="s">
+        <v>626</v>
+      </c>
+      <c r="K74" t="s">
+        <v>627</v>
+      </c>
+      <c r="L74" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" t="s">
+        <v>628</v>
+      </c>
+      <c r="B75" t="s">
+        <v>629</v>
+      </c>
+      <c r="C75" t="s">
+        <v>630</v>
+      </c>
+      <c r="D75" t="s">
+        <v>631</v>
+      </c>
+      <c r="E75" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" t="s">
+        <v>630</v>
+      </c>
+      <c r="G75" t="s">
+        <v>131</v>
+      </c>
+      <c r="H75" t="s">
+        <v>112</v>
+      </c>
+      <c r="I75" t="s">
+        <v>115</v>
+      </c>
+      <c r="J75" t="s">
+        <v>49</v>
+      </c>
+      <c r="K75" t="s">
+        <v>632</v>
+      </c>
+      <c r="L75" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" t="s">
+        <v>633</v>
+      </c>
+      <c r="B76" t="s">
+        <v>634</v>
+      </c>
+      <c r="C76" t="s">
+        <v>635</v>
+      </c>
+      <c r="D76" t="s">
+        <v>636</v>
+      </c>
+      <c r="E76" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" t="s">
+        <v>635</v>
+      </c>
+      <c r="G76" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" t="s">
+        <v>156</v>
+      </c>
+      <c r="I76" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s">
+        <v>371</v>
+      </c>
+      <c r="K76" t="s">
+        <v>637</v>
+      </c>
+      <c r="L76" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" t="s">
+        <v>639</v>
+      </c>
+      <c r="B77" t="s">
+        <v>640</v>
+      </c>
+      <c r="C77" t="s">
+        <v>641</v>
+      </c>
+      <c r="D77" t="s">
+        <v>642</v>
+      </c>
+      <c r="E77" t="s">
+        <v>643</v>
+      </c>
+      <c r="F77" t="s">
+        <v>598</v>
+      </c>
+      <c r="G77" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" t="s">
+        <v>644</v>
+      </c>
+      <c r="I77" t="s">
+        <v>59</v>
+      </c>
+      <c r="J77" t="s">
+        <v>645</v>
+      </c>
+      <c r="K77" t="s">
+        <v>646</v>
+      </c>
+      <c r="L77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>647</v>
+      </c>
+      <c r="B78" t="s">
+        <v>648</v>
+      </c>
+      <c r="C78" t="s">
+        <v>431</v>
+      </c>
+      <c r="D78" t="s">
+        <v>649</v>
+      </c>
+      <c r="E78" t="s">
+        <v>433</v>
+      </c>
+      <c r="F78" t="s">
+        <v>393</v>
+      </c>
+      <c r="G78" t="s">
+        <v>431</v>
+      </c>
+      <c r="H78" t="s">
+        <v>289</v>
+      </c>
+      <c r="I78" t="s">
+        <v>306</v>
+      </c>
+      <c r="J78" t="s">
+        <v>650</v>
+      </c>
+      <c r="K78" t="s">
+        <v>651</v>
+      </c>
+      <c r="L78" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" t="s">
+        <v>652</v>
+      </c>
+      <c r="B79" t="s">
+        <v>653</v>
+      </c>
+      <c r="C79" t="s">
+        <v>654</v>
+      </c>
+      <c r="D79" t="s">
+        <v>655</v>
+      </c>
+      <c r="E79" t="s">
+        <v>514</v>
+      </c>
+      <c r="F79" t="s">
+        <v>656</v>
+      </c>
+      <c r="G79" t="s">
+        <v>515</v>
+      </c>
+      <c r="H79" t="s">
+        <v>512</v>
+      </c>
+      <c r="I79" t="s">
+        <v>115</v>
+      </c>
+      <c r="J79" t="s">
+        <v>517</v>
+      </c>
+      <c r="K79" t="s">
+        <v>657</v>
+      </c>
+      <c r="L79" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" t="s">
+        <v>658</v>
+      </c>
+      <c r="B80" t="s">
+        <v>659</v>
+      </c>
+      <c r="C80" t="s">
+        <v>660</v>
+      </c>
+      <c r="D80" t="s">
+        <v>661</v>
+      </c>
+      <c r="E80" t="s">
+        <v>257</v>
+      </c>
+      <c r="F80" t="s">
+        <v>258</v>
+      </c>
+      <c r="G80" t="s">
+        <v>660</v>
+      </c>
+      <c r="H80" t="s">
+        <v>404</v>
+      </c>
+      <c r="I80" t="s">
+        <v>555</v>
+      </c>
+      <c r="J80" t="s">
+        <v>662</v>
+      </c>
+      <c r="K80" t="s">
+        <v>663</v>
+      </c>
+      <c r="L80" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>664</v>
+      </c>
+      <c r="B81" t="s">
+        <v>665</v>
+      </c>
+      <c r="C81" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" t="s">
+        <v>666</v>
+      </c>
+      <c r="E81" t="s">
+        <v>158</v>
+      </c>
+      <c r="F81" t="s">
+        <v>159</v>
+      </c>
+      <c r="G81" t="s">
+        <v>156</v>
+      </c>
+      <c r="H81" t="s">
+        <v>370</v>
+      </c>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s">
+        <v>667</v>
+      </c>
+      <c r="K81" t="s">
+        <v>668</v>
+      </c>
+      <c r="L81" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>669</v>
+      </c>
+      <c r="B82" t="s">
+        <v>670</v>
+      </c>
+      <c r="C82" t="s">
+        <v>671</v>
+      </c>
+      <c r="D82" t="s">
+        <v>672</v>
+      </c>
+      <c r="E82" t="s">
+        <v>673</v>
+      </c>
+      <c r="F82" t="s">
+        <v>671</v>
+      </c>
+      <c r="G82" t="s">
+        <v>674</v>
+      </c>
+      <c r="H82" t="s">
+        <v>675</v>
+      </c>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s">
+        <v>676</v>
+      </c>
+      <c r="K82" t="s">
+        <v>677</v>
+      </c>
+      <c r="L82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>678</v>
+      </c>
+      <c r="B83" t="s">
+        <v>679</v>
+      </c>
+      <c r="C83" t="s">
+        <v>680</v>
+      </c>
+      <c r="D83" t="s">
+        <v>681</v>
+      </c>
+      <c r="E83" t="s">
+        <v>349</v>
+      </c>
+      <c r="F83" t="s">
+        <v>347</v>
+      </c>
+      <c r="G83" t="s">
+        <v>680</v>
+      </c>
+      <c r="H83" t="s">
+        <v>682</v>
+      </c>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s">
+        <v>683</v>
+      </c>
+      <c r="K83" t="s">
+        <v>684</v>
+      </c>
+      <c r="L83" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>686</v>
+      </c>
+      <c r="B84" t="s">
+        <v>687</v>
+      </c>
+      <c r="C84" t="s">
+        <v>688</v>
+      </c>
+      <c r="D84" t="s">
+        <v>689</v>
+      </c>
+      <c r="E84" t="s">
+        <v>690</v>
+      </c>
+      <c r="F84" t="s">
+        <v>688</v>
+      </c>
+      <c r="G84" t="s">
+        <v>221</v>
+      </c>
+      <c r="H84" t="s">
+        <v>69</v>
+      </c>
+      <c r="I84" t="s">
+        <v>59</v>
+      </c>
+      <c r="J84" t="s">
+        <v>371</v>
+      </c>
+      <c r="K84" t="s">
+        <v>691</v>
+      </c>
+      <c r="L84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>692</v>
+      </c>
+      <c r="B85" t="s">
+        <v>693</v>
+      </c>
+      <c r="C85" t="s">
+        <v>694</v>
+      </c>
+      <c r="D85" t="s">
+        <v>695</v>
+      </c>
+      <c r="E85" t="s">
+        <v>696</v>
+      </c>
+      <c r="F85" t="s">
+        <v>697</v>
+      </c>
+      <c r="G85" t="s">
+        <v>698</v>
+      </c>
+      <c r="H85" t="s">
+        <v>699</v>
+      </c>
+      <c r="I85" t="s">
+        <v>625</v>
+      </c>
+      <c r="J85" t="s">
+        <v>700</v>
+      </c>
+      <c r="K85" t="s">
+        <v>701</v>
+      </c>
+      <c r="L85" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>702</v>
+      </c>
+      <c r="B86" t="s">
+        <v>703</v>
+      </c>
+      <c r="C86" t="s">
+        <v>704</v>
+      </c>
+      <c r="D86" t="s">
+        <v>705</v>
+      </c>
+      <c r="E86" t="s">
+        <v>355</v>
+      </c>
+      <c r="F86" t="s">
+        <v>359</v>
+      </c>
+      <c r="G86" t="s">
+        <v>472</v>
+      </c>
+      <c r="H86" t="s">
+        <v>706</v>
+      </c>
+      <c r="I86" t="s">
+        <v>59</v>
+      </c>
+      <c r="J86" t="s">
+        <v>707</v>
+      </c>
+      <c r="K86" t="s">
+        <v>708</v>
+      </c>
+      <c r="L86" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>362</v>
+      </c>
+      <c r="B87" t="s">
+        <v>363</v>
+      </c>
+      <c r="C87" t="s">
+        <v>277</v>
+      </c>
+      <c r="D87" t="s">
+        <v>364</v>
+      </c>
+      <c r="E87" t="s">
+        <v>278</v>
+      </c>
+      <c r="F87" t="s">
+        <v>274</v>
+      </c>
+      <c r="G87" t="s">
+        <v>277</v>
+      </c>
+      <c r="H87" t="s">
+        <v>365</v>
+      </c>
+      <c r="I87" t="s">
+        <v>279</v>
+      </c>
+      <c r="J87" t="s">
+        <v>143</v>
+      </c>
+      <c r="K87" t="s">
+        <v>709</v>
+      </c>
+      <c r="L87" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>710</v>
+      </c>
+      <c r="B88" t="s">
+        <v>711</v>
+      </c>
+      <c r="C88" t="s">
+        <v>712</v>
+      </c>
+      <c r="D88" t="s">
+        <v>713</v>
+      </c>
+      <c r="E88" t="s">
+        <v>458</v>
+      </c>
+      <c r="F88" t="s">
+        <v>712</v>
+      </c>
+      <c r="G88" t="s">
+        <v>714</v>
+      </c>
+      <c r="H88" t="s">
+        <v>715</v>
+      </c>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s">
+        <v>716</v>
+      </c>
+      <c r="K88" t="s">
+        <v>717</v>
+      </c>
+      <c r="L88" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>719</v>
+      </c>
+      <c r="B89" t="s">
+        <v>720</v>
+      </c>
+      <c r="C89" t="s">
+        <v>721</v>
+      </c>
+      <c r="D89" t="s">
+        <v>722</v>
+      </c>
+      <c r="E89" t="s">
+        <v>274</v>
+      </c>
+      <c r="F89" t="s">
+        <v>721</v>
+      </c>
+      <c r="G89" t="s">
+        <v>278</v>
+      </c>
+      <c r="H89" t="s">
+        <v>277</v>
+      </c>
+      <c r="I89" t="s">
+        <v>279</v>
+      </c>
+      <c r="J89" t="s">
+        <v>723</v>
+      </c>
+      <c r="K89" t="s">
+        <v>724</v>
+      </c>
+      <c r="L89" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>725</v>
+      </c>
+      <c r="B90" t="s">
+        <v>726</v>
+      </c>
+      <c r="C90" t="s">
+        <v>727</v>
+      </c>
+      <c r="D90" t="s">
+        <v>728</v>
+      </c>
+      <c r="E90" t="s">
+        <v>729</v>
+      </c>
+      <c r="F90" t="s">
+        <v>730</v>
+      </c>
+      <c r="G90" t="s">
+        <v>731</v>
+      </c>
+      <c r="H90" t="s">
+        <v>46</v>
+      </c>
+      <c r="I90" t="s">
+        <v>115</v>
+      </c>
+      <c r="J90" t="s">
+        <v>732</v>
+      </c>
+      <c r="K90" t="s">
+        <v>733</v>
+      </c>
+      <c r="L90" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>734</v>
+      </c>
+      <c r="B91" t="s">
+        <v>735</v>
+      </c>
+      <c r="C91" t="s">
+        <v>736</v>
+      </c>
+      <c r="D91" t="s">
+        <v>737</v>
+      </c>
+      <c r="E91" t="s">
+        <v>738</v>
+      </c>
+      <c r="F91" t="s">
+        <v>220</v>
+      </c>
+      <c r="G91" t="s">
+        <v>739</v>
+      </c>
+      <c r="H91" t="s">
+        <v>740</v>
+      </c>
+      <c r="I91" t="s">
+        <v>59</v>
+      </c>
+      <c r="J91" t="s">
+        <v>741</v>
+      </c>
+      <c r="K91" t="s">
+        <v>742</v>
+      </c>
+      <c r="L91" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>743</v>
+      </c>
+      <c r="B92" t="s">
+        <v>744</v>
+      </c>
+      <c r="C92" t="s">
+        <v>745</v>
+      </c>
+      <c r="D92" t="s">
+        <v>746</v>
+      </c>
+      <c r="E92" t="s">
+        <v>747</v>
+      </c>
+      <c r="F92" t="s">
+        <v>748</v>
+      </c>
+      <c r="G92" t="s">
+        <v>58</v>
+      </c>
+      <c r="H92" t="s">
+        <v>221</v>
+      </c>
+      <c r="I92" t="s">
+        <v>59</v>
+      </c>
+      <c r="J92" t="s">
+        <v>96</v>
+      </c>
+      <c r="K92" t="s">
+        <v>749</v>
+      </c>
+      <c r="L92" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>750</v>
+      </c>
+      <c r="B93" t="s">
+        <v>751</v>
+      </c>
+      <c r="C93" t="s">
+        <v>752</v>
+      </c>
+      <c r="D93" t="s">
+        <v>753</v>
+      </c>
+      <c r="E93" t="s">
+        <v>274</v>
+      </c>
+      <c r="F93" t="s">
+        <v>752</v>
+      </c>
+      <c r="G93" t="s">
+        <v>277</v>
+      </c>
+      <c r="H93" t="s">
+        <v>278</v>
+      </c>
+      <c r="I93" t="s">
+        <v>279</v>
+      </c>
+      <c r="J93" t="s">
+        <v>754</v>
+      </c>
+      <c r="K93" t="s">
+        <v>755</v>
+      </c>
+      <c r="L93" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>756</v>
+      </c>
+      <c r="B94" t="s">
+        <v>757</v>
+      </c>
+      <c r="C94" t="s">
+        <v>758</v>
+      </c>
+      <c r="D94" t="s">
+        <v>759</v>
+      </c>
+      <c r="E94" t="s">
+        <v>760</v>
+      </c>
+      <c r="F94" t="s">
+        <v>758</v>
+      </c>
+      <c r="G94" t="s">
+        <v>761</v>
+      </c>
+      <c r="H94" t="s">
+        <v>762</v>
+      </c>
+      <c r="I94" t="s">
+        <v>59</v>
+      </c>
+      <c r="J94" t="s">
+        <v>434</v>
+      </c>
+      <c r="K94" t="s">
+        <v>763</v>
+      </c>
+      <c r="L94" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>764</v>
+      </c>
+      <c r="B95" t="s">
+        <v>764</v>
+      </c>
+      <c r="C95" t="s">
+        <v>765</v>
+      </c>
+      <c r="D95" t="s">
+        <v>766</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95" t="s">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s">
+        <v>765</v>
+      </c>
+      <c r="H95" t="s">
+        <v>239</v>
+      </c>
+      <c r="I95" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s">
+        <v>38</v>
+      </c>
+      <c r="K95" t="s">
+        <v>767</v>
+      </c>
+      <c r="L95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>768</v>
+      </c>
+      <c r="B96" t="s">
+        <v>769</v>
+      </c>
+      <c r="C96" t="s">
+        <v>770</v>
+      </c>
+      <c r="D96" t="s">
+        <v>771</v>
+      </c>
+      <c r="E96" t="s">
+        <v>772</v>
+      </c>
+      <c r="F96" t="s">
+        <v>770</v>
+      </c>
+      <c r="G96" t="s">
+        <v>56</v>
+      </c>
+      <c r="H96" t="s">
+        <v>690</v>
+      </c>
+      <c r="I96" t="s">
+        <v>59</v>
+      </c>
+      <c r="J96" t="s">
+        <v>222</v>
+      </c>
+      <c r="K96" t="s">
+        <v>773</v>
+      </c>
+      <c r="L96" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>774</v>
+      </c>
+      <c r="B97" t="s">
+        <v>774</v>
+      </c>
+      <c r="C97" t="s">
+        <v>775</v>
+      </c>
+      <c r="D97" t="s">
+        <v>776</v>
+      </c>
+      <c r="E97" t="s">
+        <v>777</v>
+      </c>
+      <c r="F97" t="s">
+        <v>775</v>
+      </c>
+      <c r="G97" t="s">
+        <v>778</v>
+      </c>
+      <c r="H97" t="s">
+        <v>779</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s">
+        <v>780</v>
+      </c>
+      <c r="K97" t="s">
+        <v>781</v>
+      </c>
+      <c r="L97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>782</v>
+      </c>
+      <c r="B98" t="s">
+        <v>783</v>
+      </c>
+      <c r="C98" t="s">
+        <v>784</v>
+      </c>
+      <c r="D98" t="s">
+        <v>785</v>
+      </c>
+      <c r="E98" t="s">
+        <v>786</v>
+      </c>
+      <c r="F98" t="s">
+        <v>787</v>
+      </c>
+      <c r="G98" t="s">
+        <v>784</v>
+      </c>
+      <c r="H98" t="s">
+        <v>788</v>
+      </c>
+      <c r="I98" t="s">
+        <v>306</v>
+      </c>
+      <c r="J98" t="s">
+        <v>645</v>
+      </c>
+      <c r="K98" t="s">
+        <v>789</v>
+      </c>
+      <c r="L98" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>790</v>
+      </c>
+      <c r="B99" t="s">
+        <v>791</v>
+      </c>
+      <c r="C99" t="s">
+        <v>792</v>
+      </c>
+      <c r="D99" t="s">
+        <v>793</v>
+      </c>
+      <c r="E99" t="s">
+        <v>794</v>
+      </c>
+      <c r="F99" t="s">
+        <v>792</v>
+      </c>
+      <c r="G99" t="s">
+        <v>268</v>
+      </c>
+      <c r="H99" t="s">
+        <v>440</v>
+      </c>
+      <c r="I99" t="s">
+        <v>115</v>
+      </c>
+      <c r="J99" t="s">
+        <v>795</v>
+      </c>
+      <c r="K99" t="s">
+        <v>796</v>
+      </c>
+      <c r="L99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>797</v>
+      </c>
+      <c r="B100" t="s">
+        <v>798</v>
+      </c>
+      <c r="C100" t="s">
+        <v>799</v>
+      </c>
+      <c r="D100" t="s">
+        <v>800</v>
+      </c>
+      <c r="E100" t="s">
+        <v>801</v>
+      </c>
+      <c r="F100" t="s">
+        <v>799</v>
+      </c>
+      <c r="G100" t="s">
+        <v>199</v>
+      </c>
+      <c r="H100" t="s">
+        <v>59</v>
+      </c>
+      <c r="I100" t="s">
+        <v>650</v>
+      </c>
+      <c r="J100" t="s">
+        <v>802</v>
+      </c>
+      <c r="K100" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>803</v>
+      </c>
+      <c r="B101" t="s">
+        <v>804</v>
+      </c>
+      <c r="C101" t="s">
+        <v>805</v>
+      </c>
+      <c r="D101" t="s">
+        <v>806</v>
+      </c>
+      <c r="E101" t="s">
+        <v>159</v>
+      </c>
+      <c r="F101" t="s">
+        <v>156</v>
+      </c>
+      <c r="G101" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" t="s">
+        <v>370</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s">
+        <v>161</v>
+      </c>
+      <c r="K101" t="s">
+        <v>807</v>
+      </c>
+      <c r="L101" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>808</v>
+      </c>
+      <c r="B102" t="s">
+        <v>809</v>
+      </c>
+      <c r="C102" t="s">
+        <v>41</v>
+      </c>
+      <c r="D102" t="s">
+        <v>810</v>
+      </c>
+      <c r="E102" t="s">
+        <v>811</v>
+      </c>
+      <c r="F102" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" t="s">
+        <v>812</v>
+      </c>
+      <c r="H102" t="s">
+        <v>46</v>
+      </c>
+      <c r="I102" t="s">
+        <v>48</v>
+      </c>
+      <c r="J102" t="s">
+        <v>813</v>
+      </c>
+      <c r="K102" t="s">
+        <v>814</v>
+      </c>
+      <c r="L102" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>815</v>
+      </c>
+      <c r="B103" t="s">
+        <v>816</v>
+      </c>
+      <c r="C103" t="s">
+        <v>817</v>
+      </c>
+      <c r="D103" t="s">
+        <v>818</v>
+      </c>
+      <c r="E103" t="s">
+        <v>260</v>
+      </c>
+      <c r="F103" t="s">
+        <v>819</v>
+      </c>
+      <c r="G103" t="s">
+        <v>820</v>
+      </c>
+      <c r="H103" t="s">
+        <v>821</v>
+      </c>
+      <c r="I103" t="s">
+        <v>555</v>
+      </c>
+      <c r="J103" t="s">
+        <v>261</v>
+      </c>
+      <c r="K103" t="s">
+        <v>822</v>
+      </c>
+      <c r="L103" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>823</v>
+      </c>
+      <c r="B104" t="s">
+        <v>824</v>
+      </c>
+      <c r="C104" t="s">
+        <v>712</v>
+      </c>
+      <c r="D104" t="s">
+        <v>825</v>
+      </c>
+      <c r="E104" t="s">
+        <v>458</v>
+      </c>
+      <c r="F104" t="s">
+        <v>712</v>
+      </c>
+      <c r="G104" t="s">
+        <v>714</v>
+      </c>
+      <c r="H104" t="s">
+        <v>715</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
+        <v>716</v>
+      </c>
+      <c r="K104" t="s">
+        <v>826</v>
+      </c>
+      <c r="L104" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>347</v>
+      </c>
+      <c r="B105" t="s">
+        <v>827</v>
+      </c>
+      <c r="C105" t="s">
+        <v>828</v>
+      </c>
+      <c r="D105" t="s">
+        <v>829</v>
+      </c>
+      <c r="E105" t="s">
+        <v>514</v>
+      </c>
+      <c r="F105" t="s">
+        <v>828</v>
+      </c>
+      <c r="G105" t="s">
+        <v>515</v>
+      </c>
+      <c r="H105" t="s">
+        <v>516</v>
+      </c>
+      <c r="I105" t="s">
+        <v>306</v>
+      </c>
+      <c r="J105" t="s">
+        <v>517</v>
+      </c>
+      <c r="K105" t="s">
+        <v>830</v>
+      </c>
+      <c r="L105" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>831</v>
+      </c>
+      <c r="B106" t="s">
+        <v>832</v>
+      </c>
+      <c r="C106" t="s">
+        <v>833</v>
+      </c>
+      <c r="D106" t="s">
+        <v>834</v>
+      </c>
+      <c r="E106" t="s">
+        <v>835</v>
+      </c>
+      <c r="F106" t="s">
+        <v>836</v>
+      </c>
+      <c r="G106" t="s">
+        <v>833</v>
+      </c>
+      <c r="H106" t="s">
+        <v>837</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s">
+        <v>297</v>
+      </c>
+      <c r="K106" t="s">
+        <v>838</v>
+      </c>
+      <c r="L106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>839</v>
+      </c>
+      <c r="B107" t="s">
+        <v>840</v>
+      </c>
+      <c r="C107" t="s">
+        <v>841</v>
+      </c>
+      <c r="D107" t="s">
+        <v>842</v>
+      </c>
+      <c r="E107" t="s">
+        <v>843</v>
+      </c>
+      <c r="F107" t="s">
+        <v>844</v>
+      </c>
+      <c r="G107" t="s">
+        <v>845</v>
+      </c>
+      <c r="H107" t="s">
+        <v>846</v>
+      </c>
+      <c r="I107" t="s">
+        <v>555</v>
+      </c>
+      <c r="J107" t="s">
+        <v>847</v>
+      </c>
+      <c r="K107" t="s">
+        <v>848</v>
+      </c>
+      <c r="L107" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>849</v>
+      </c>
+      <c r="B108" t="s">
+        <v>850</v>
+      </c>
+      <c r="C108" t="s">
+        <v>851</v>
+      </c>
+      <c r="D108" t="s">
+        <v>852</v>
+      </c>
+      <c r="E108" t="s">
+        <v>853</v>
+      </c>
+      <c r="F108" t="s">
+        <v>851</v>
+      </c>
+      <c r="G108" t="s">
+        <v>854</v>
+      </c>
+      <c r="H108" t="s">
+        <v>855</v>
+      </c>
+      <c r="I108" t="s">
+        <v>482</v>
+      </c>
+      <c r="J108" t="s">
+        <v>856</v>
+      </c>
+      <c r="K108" t="s">
+        <v>857</v>
+      </c>
+      <c r="L108" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>858</v>
+      </c>
+      <c r="B109" t="s">
+        <v>859</v>
+      </c>
+      <c r="C109" t="s">
+        <v>860</v>
+      </c>
+      <c r="D109" t="s">
+        <v>861</v>
+      </c>
+      <c r="E109" t="s">
+        <v>862</v>
+      </c>
+      <c r="F109" t="s">
+        <v>863</v>
+      </c>
+      <c r="G109" t="s">
+        <v>864</v>
+      </c>
+      <c r="H109" t="s">
+        <v>865</v>
+      </c>
+      <c r="I109" t="s">
+        <v>866</v>
+      </c>
+      <c r="J109" t="s">
+        <v>741</v>
+      </c>
+      <c r="K109" t="s">
+        <v>867</v>
+      </c>
+      <c r="L109" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>869</v>
+      </c>
+      <c r="B110" t="s">
+        <v>870</v>
+      </c>
+      <c r="C110" t="s">
+        <v>871</v>
+      </c>
+      <c r="D110" t="s">
+        <v>872</v>
+      </c>
+      <c r="E110" t="s">
+        <v>566</v>
+      </c>
+      <c r="F110" t="s">
+        <v>871</v>
+      </c>
+      <c r="G110" t="s">
+        <v>569</v>
+      </c>
+      <c r="H110" t="s">
+        <v>873</v>
+      </c>
+      <c r="I110" t="s">
+        <v>625</v>
+      </c>
+      <c r="J110" t="s">
+        <v>570</v>
+      </c>
+      <c r="K110" t="s">
+        <v>874</v>
+      </c>
+      <c r="L110" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="A111" t="s">
+        <v>875</v>
+      </c>
+      <c r="B111" t="s">
+        <v>876</v>
+      </c>
+      <c r="C111" t="s">
+        <v>877</v>
+      </c>
+      <c r="D111" t="s">
+        <v>878</v>
+      </c>
+      <c r="E111" t="s">
+        <v>249</v>
+      </c>
+      <c r="F111" t="s">
+        <v>879</v>
+      </c>
+      <c r="G111" t="s">
+        <v>221</v>
+      </c>
+      <c r="H111" t="s">
+        <v>376</v>
+      </c>
+      <c r="I111" t="s">
+        <v>59</v>
+      </c>
+      <c r="J111" t="s">
+        <v>880</v>
+      </c>
+      <c r="K111" t="s">
+        <v>881</v>
+      </c>
+      <c r="L111" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
